--- a/output/2024_A24_SECCION_E.xlsx
+++ b/output/2024_A24_SECCION_E.xlsx
@@ -209,16 +209,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -234,7 +226,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -242,30 +234,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,54 +538,54 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>25533</v>
       </c>
       <c r="B2" t="s">
@@ -661,7 +635,7 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>31450</v>
       </c>
       <c r="B3" t="s">
@@ -708,7 +682,7 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>31451</v>
       </c>
       <c r="B4" t="s">
@@ -755,7 +729,7 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>31452</v>
       </c>
       <c r="B5" t="s">
@@ -802,7 +776,7 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>31453</v>
       </c>
       <c r="B6" t="s">
@@ -852,7 +826,7 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>43748</v>
       </c>
       <c r="B7" t="s">
@@ -902,7 +876,7 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>43749</v>
       </c>
       <c r="B8" t="s">
@@ -949,7 +923,7 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>43750</v>
       </c>
       <c r="B9" t="s">
@@ -996,7 +970,7 @@
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>43751</v>
       </c>
       <c r="B10" t="s">
@@ -1043,7 +1017,7 @@
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>43752</v>
       </c>
       <c r="B11" t="s">
@@ -1093,7 +1067,7 @@
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>48176</v>
       </c>
       <c r="B12" t="s">
@@ -1143,7 +1117,7 @@
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>48177</v>
       </c>
       <c r="B13" t="s">
@@ -1190,7 +1164,7 @@
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>49062</v>
       </c>
       <c r="B14" t="s">
@@ -1240,7 +1214,7 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>49063</v>
       </c>
       <c r="B15" t="s">
@@ -1287,7 +1261,7 @@
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>49064</v>
       </c>
       <c r="B16" t="s">
@@ -1337,7 +1311,7 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>195157</v>
       </c>
       <c r="B17" t="s">
@@ -1387,7 +1361,7 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>195158</v>
       </c>
       <c r="B18" t="s">
@@ -1434,7 +1408,7 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>195159</v>
       </c>
       <c r="B19" t="s">
@@ -1481,7 +1455,7 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>200289</v>
       </c>
       <c r="B20" t="s">
@@ -1531,7 +1505,7 @@
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>200290</v>
       </c>
       <c r="B21" t="s">
@@ -1581,7 +1555,7 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>200291</v>
       </c>
       <c r="B22" t="s">
@@ -1631,7 +1605,7 @@
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>207335</v>
       </c>
       <c r="B23" t="s">
@@ -1681,7 +1655,7 @@
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>207336</v>
       </c>
       <c r="B24" t="s">
@@ -1728,7 +1702,7 @@
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>207337</v>
       </c>
       <c r="B25" t="s">
@@ -1775,7 +1749,7 @@
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>207338</v>
       </c>
       <c r="B26" t="s">
@@ -1822,7 +1796,7 @@
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>207339</v>
       </c>
       <c r="B27" t="s">
@@ -1869,7 +1843,7 @@
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>207340</v>
       </c>
       <c r="B28" t="s">
@@ -1919,7 +1893,7 @@
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>228697</v>
       </c>
       <c r="B29" t="s">
@@ -1969,7 +1943,7 @@
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>228698</v>
       </c>
       <c r="B30" t="s">
@@ -2016,7 +1990,7 @@
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>228699</v>
       </c>
       <c r="B31" t="s">
@@ -2063,7 +2037,7 @@
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>228700</v>
       </c>
       <c r="B32" t="s">
@@ -2113,7 +2087,7 @@
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>437572</v>
       </c>
       <c r="B33" t="s">
@@ -2160,7 +2134,7 @@
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>437573</v>
       </c>
       <c r="B34" t="s">
@@ -2210,7 +2184,7 @@
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>721224</v>
       </c>
       <c r="B35" t="s">
@@ -2260,7 +2234,7 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>721226</v>
       </c>
       <c r="B36" t="s">
@@ -2310,7 +2284,7 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>1626983</v>
       </c>
       <c r="B37" t="s">
@@ -2360,7 +2334,7 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>1626985</v>
       </c>
       <c r="B38" t="s">
@@ -2407,7 +2381,7 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>1626987</v>
       </c>
       <c r="B39" t="s">
@@ -2454,7 +2428,7 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>1626989</v>
       </c>
       <c r="B40" t="s">
@@ -2501,7 +2475,7 @@
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>1626991</v>
       </c>
       <c r="B41" t="s">
@@ -2551,7 +2525,7 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>1627848</v>
       </c>
       <c r="B42" t="s">
@@ -2601,7 +2575,7 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="1">
+      <c r="A43">
         <v>1627850</v>
       </c>
       <c r="B43" t="s">
@@ -2651,7 +2625,7 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>1627852</v>
       </c>
       <c r="B44" t="s">
@@ -2698,7 +2672,7 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="1">
+      <c r="A45">
         <v>1627854</v>
       </c>
       <c r="B45" t="s">
@@ -2748,7 +2722,7 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>1700014</v>
       </c>
       <c r="B46" t="s">
@@ -2798,7 +2772,7 @@
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="1">
+      <c r="A47">
         <v>1700015</v>
       </c>
       <c r="B47" t="s">
@@ -2848,7 +2822,7 @@
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" s="1">
+      <c r="A48">
         <v>1700069</v>
       </c>
       <c r="B48" t="s">
@@ -2898,7 +2872,7 @@
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="1">
+      <c r="A49">
         <v>1700070</v>
       </c>
       <c r="B49" t="s">
@@ -2948,7 +2922,7 @@
       </c>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="1">
+      <c r="A50">
         <v>1700071</v>
       </c>
       <c r="B50" t="s">
@@ -2998,7 +2972,7 @@
       </c>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="1">
+      <c r="A51">
         <v>1700843</v>
       </c>
       <c r="B51" t="s">
@@ -3048,7 +3022,7 @@
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>1700844</v>
       </c>
       <c r="B52" t="s">
@@ -3098,7 +3072,7 @@
       </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="1">
+      <c r="A53">
         <v>1700845</v>
       </c>
       <c r="B53" t="s">
@@ -3148,7 +3122,7 @@
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="1">
+      <c r="A54">
         <v>1700853</v>
       </c>
       <c r="B54" t="s">
@@ -3198,7 +3172,7 @@
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="1">
+      <c r="A55">
         <v>1702839</v>
       </c>
       <c r="B55" t="s">
@@ -3248,7 +3222,7 @@
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="1">
+      <c r="A56">
         <v>1702840</v>
       </c>
       <c r="B56" t="s">
@@ -3298,7 +3272,7 @@
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="1">
+      <c r="A57">
         <v>1702841</v>
       </c>
       <c r="B57" t="s">
@@ -3348,7 +3322,7 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="1">
+      <c r="A58">
         <v>1702842</v>
       </c>
       <c r="B58" t="s">
@@ -3398,7 +3372,7 @@
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="1">
+      <c r="A59">
         <v>1703907</v>
       </c>
       <c r="B59" t="s">
@@ -3448,7 +3422,7 @@
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="1">
+      <c r="A60">
         <v>1703908</v>
       </c>
       <c r="B60" t="s">
@@ -3498,7 +3472,7 @@
       </c>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="1">
+      <c r="A61">
         <v>1703911</v>
       </c>
       <c r="B61" t="s">
@@ -3548,7 +3522,7 @@
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="1">
+      <c r="A62">
         <v>1703912</v>
       </c>
       <c r="B62" t="s">
@@ -3598,7 +3572,7 @@
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="1">
+      <c r="A63">
         <v>1703913</v>
       </c>
       <c r="B63" t="s">
@@ -3648,7 +3622,7 @@
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="1">
+      <c r="A64">
         <v>1704389</v>
       </c>
       <c r="B64" t="s">
@@ -3698,7 +3672,7 @@
       </c>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" s="1">
+      <c r="A65">
         <v>1704390</v>
       </c>
       <c r="B65" t="s">
@@ -3748,7 +3722,7 @@
       </c>
     </row>
     <row r="66" spans="1:16">
-      <c r="A66" s="1">
+      <c r="A66">
         <v>1704391</v>
       </c>
       <c r="B66" t="s">
@@ -3798,7 +3772,7 @@
       </c>
     </row>
     <row r="67" spans="1:16">
-      <c r="A67" s="1">
+      <c r="A67">
         <v>1704392</v>
       </c>
       <c r="B67" t="s">
@@ -3848,7 +3822,7 @@
       </c>
     </row>
     <row r="68" spans="1:16">
-      <c r="A68" s="1">
+      <c r="A68">
         <v>1704393</v>
       </c>
       <c r="B68" t="s">
@@ -3898,7 +3872,7 @@
       </c>
     </row>
     <row r="69" spans="1:16">
-      <c r="A69" s="1">
+      <c r="A69">
         <v>1704637</v>
       </c>
       <c r="B69" t="s">
@@ -3948,7 +3922,7 @@
       </c>
     </row>
     <row r="70" spans="1:16">
-      <c r="A70" s="1">
+      <c r="A70">
         <v>1704638</v>
       </c>
       <c r="B70" t="s">
@@ -3998,7 +3972,7 @@
       </c>
     </row>
     <row r="71" spans="1:16">
-      <c r="A71" s="1">
+      <c r="A71">
         <v>1704639</v>
       </c>
       <c r="B71" t="s">
@@ -4048,7 +4022,7 @@
       </c>
     </row>
     <row r="72" spans="1:16">
-      <c r="A72" s="1">
+      <c r="A72">
         <v>1704640</v>
       </c>
       <c r="B72" t="s">
@@ -4098,7 +4072,7 @@
       </c>
     </row>
     <row r="73" spans="1:16">
-      <c r="A73" s="1">
+      <c r="A73">
         <v>1704871</v>
       </c>
       <c r="B73" t="s">
@@ -4148,7 +4122,7 @@
       </c>
     </row>
     <row r="74" spans="1:16">
-      <c r="A74" s="1">
+      <c r="A74">
         <v>1704872</v>
       </c>
       <c r="B74" t="s">
@@ -4198,7 +4172,7 @@
       </c>
     </row>
     <row r="75" spans="1:16">
-      <c r="A75" s="1">
+      <c r="A75">
         <v>1704873</v>
       </c>
       <c r="B75" t="s">
@@ -4248,7 +4222,7 @@
       </c>
     </row>
     <row r="76" spans="1:16">
-      <c r="A76" s="1">
+      <c r="A76">
         <v>1704874</v>
       </c>
       <c r="B76" t="s">
@@ -4298,7 +4272,7 @@
       </c>
     </row>
     <row r="77" spans="1:16">
-      <c r="A77" s="1">
+      <c r="A77">
         <v>1705384</v>
       </c>
       <c r="B77" t="s">
@@ -4348,7 +4322,7 @@
       </c>
     </row>
     <row r="78" spans="1:16">
-      <c r="A78" s="1">
+      <c r="A78">
         <v>1705385</v>
       </c>
       <c r="B78" t="s">
@@ -4398,7 +4372,7 @@
       </c>
     </row>
     <row r="79" spans="1:16">
-      <c r="A79" s="1">
+      <c r="A79">
         <v>1705386</v>
       </c>
       <c r="B79" t="s">
@@ -4448,7 +4422,7 @@
       </c>
     </row>
     <row r="80" spans="1:16">
-      <c r="A80" s="1">
+      <c r="A80">
         <v>1705387</v>
       </c>
       <c r="B80" t="s">
@@ -4498,7 +4472,7 @@
       </c>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" s="1">
+      <c r="A81">
         <v>1707733</v>
       </c>
       <c r="B81" t="s">
@@ -4548,7 +4522,7 @@
       </c>
     </row>
     <row r="82" spans="1:16">
-      <c r="A82" s="1">
+      <c r="A82">
         <v>1707734</v>
       </c>
       <c r="B82" t="s">
@@ -4598,7 +4572,7 @@
       </c>
     </row>
     <row r="83" spans="1:16">
-      <c r="A83" s="1">
+      <c r="A83">
         <v>1707735</v>
       </c>
       <c r="B83" t="s">
@@ -4648,7 +4622,7 @@
       </c>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" s="1">
+      <c r="A84">
         <v>1707736</v>
       </c>
       <c r="B84" t="s">
@@ -4698,7 +4672,7 @@
       </c>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="1">
+      <c r="A85">
         <v>1707946</v>
       </c>
       <c r="B85" t="s">
@@ -4748,7 +4722,7 @@
       </c>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" s="1">
+      <c r="A86">
         <v>1707947</v>
       </c>
       <c r="B86" t="s">
@@ -4798,7 +4772,7 @@
       </c>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" s="1">
+      <c r="A87">
         <v>1707948</v>
       </c>
       <c r="B87" t="s">
@@ -4848,7 +4822,7 @@
       </c>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" s="1">
+      <c r="A88">
         <v>1708056</v>
       </c>
       <c r="B88" t="s">
@@ -4898,7 +4872,7 @@
       </c>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" s="1">
+      <c r="A89">
         <v>1708057</v>
       </c>
       <c r="B89" t="s">
@@ -4948,7 +4922,7 @@
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="1">
+      <c r="A90">
         <v>1710154</v>
       </c>
       <c r="B90" t="s">
@@ -4998,7 +4972,7 @@
       </c>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="1">
+      <c r="A91">
         <v>1710160</v>
       </c>
       <c r="B91" t="s">
@@ -5048,7 +5022,7 @@
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="1">
+      <c r="A92">
         <v>1710179</v>
       </c>
       <c r="B92" t="s">
@@ -5098,7 +5072,7 @@
       </c>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="1">
+      <c r="A93">
         <v>1710199</v>
       </c>
       <c r="B93" t="s">
@@ -5148,7 +5122,7 @@
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="1">
+      <c r="A94">
         <v>1710200</v>
       </c>
       <c r="B94" t="s">
@@ -5198,7 +5172,7 @@
       </c>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="1">
+      <c r="A95">
         <v>1713926</v>
       </c>
       <c r="B95" t="s">
@@ -5248,7 +5222,7 @@
       </c>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="1">
+      <c r="A96">
         <v>1713927</v>
       </c>
       <c r="B96" t="s">
@@ -5298,7 +5272,7 @@
       </c>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="1">
+      <c r="A97">
         <v>1713928</v>
       </c>
       <c r="B97" t="s">
@@ -5348,7 +5322,7 @@
       </c>
     </row>
     <row r="98" spans="1:16">
-      <c r="A98" s="1">
+      <c r="A98">
         <v>1713929</v>
       </c>
       <c r="B98" t="s">
@@ -5398,7 +5372,7 @@
       </c>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" s="1">
+      <c r="A99">
         <v>1713930</v>
       </c>
       <c r="B99" t="s">
@@ -5448,7 +5422,7 @@
       </c>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" s="1">
+      <c r="A100">
         <v>2134961</v>
       </c>
       <c r="B100" t="s">
@@ -5498,7 +5472,7 @@
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" s="1">
+      <c r="A101">
         <v>2134962</v>
       </c>
       <c r="B101" t="s">
@@ -5545,7 +5519,7 @@
       </c>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" s="1">
+      <c r="A102">
         <v>2134963</v>
       </c>
       <c r="B102" t="s">
@@ -5592,7 +5566,7 @@
       </c>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" s="1">
+      <c r="A103">
         <v>2134964</v>
       </c>
       <c r="B103" t="s">
@@ -5642,7 +5616,7 @@
       </c>
     </row>
     <row r="104" spans="1:16">
-      <c r="A104" s="1">
+      <c r="A104">
         <v>2135388</v>
       </c>
       <c r="B104" t="s">
@@ -5692,7 +5666,7 @@
       </c>
     </row>
     <row r="105" spans="1:16">
-      <c r="A105" s="1">
+      <c r="A105">
         <v>2135389</v>
       </c>
       <c r="B105" t="s">
@@ -5739,7 +5713,7 @@
       </c>
     </row>
     <row r="106" spans="1:16">
-      <c r="A106" s="1">
+      <c r="A106">
         <v>2135390</v>
       </c>
       <c r="B106" t="s">
@@ -5786,7 +5760,7 @@
       </c>
     </row>
     <row r="107" spans="1:16">
-      <c r="A107" s="1">
+      <c r="A107">
         <v>2135391</v>
       </c>
       <c r="B107" t="s">
@@ -5833,7 +5807,7 @@
       </c>
     </row>
     <row r="108" spans="1:16">
-      <c r="A108" s="1">
+      <c r="A108">
         <v>2135392</v>
       </c>
       <c r="B108" t="s">
@@ -5883,7 +5857,7 @@
       </c>
     </row>
     <row r="109" spans="1:16">
-      <c r="A109" s="1">
+      <c r="A109">
         <v>2135561</v>
       </c>
       <c r="B109" t="s">
@@ -5933,7 +5907,7 @@
       </c>
     </row>
     <row r="110" spans="1:16">
-      <c r="A110" s="1">
+      <c r="A110">
         <v>2135562</v>
       </c>
       <c r="B110" t="s">
@@ -5980,7 +5954,7 @@
       </c>
     </row>
     <row r="111" spans="1:16">
-      <c r="A111" s="1">
+      <c r="A111">
         <v>2135563</v>
       </c>
       <c r="B111" t="s">
@@ -6030,7 +6004,7 @@
       </c>
     </row>
     <row r="112" spans="1:16">
-      <c r="A112" s="1">
+      <c r="A112">
         <v>2135564</v>
       </c>
       <c r="B112" t="s">
@@ -6080,7 +6054,7 @@
       </c>
     </row>
     <row r="113" spans="1:16">
-      <c r="A113" s="1">
+      <c r="A113">
         <v>2266994</v>
       </c>
       <c r="B113" t="s">
@@ -6130,7 +6104,7 @@
       </c>
     </row>
     <row r="114" spans="1:16">
-      <c r="A114" s="1">
+      <c r="A114">
         <v>2266995</v>
       </c>
       <c r="B114" t="s">
@@ -6180,7 +6154,7 @@
       </c>
     </row>
     <row r="115" spans="1:16">
-      <c r="A115" s="1">
+      <c r="A115">
         <v>2266996</v>
       </c>
       <c r="B115" t="s">
@@ -6230,7 +6204,7 @@
       </c>
     </row>
     <row r="116" spans="1:16">
-      <c r="A116" s="1">
+      <c r="A116">
         <v>2266997</v>
       </c>
       <c r="B116" t="s">
@@ -6280,7 +6254,7 @@
       </c>
     </row>
     <row r="117" spans="1:16">
-      <c r="A117" s="1">
+      <c r="A117">
         <v>2267014</v>
       </c>
       <c r="B117" t="s">
@@ -6330,7 +6304,7 @@
       </c>
     </row>
     <row r="118" spans="1:16">
-      <c r="A118" s="1">
+      <c r="A118">
         <v>2267015</v>
       </c>
       <c r="B118" t="s">
@@ -6380,7 +6354,7 @@
       </c>
     </row>
     <row r="119" spans="1:16">
-      <c r="A119" s="1">
+      <c r="A119">
         <v>2267148</v>
       </c>
       <c r="B119" t="s">
@@ -6430,7 +6404,7 @@
       </c>
     </row>
     <row r="120" spans="1:16">
-      <c r="A120" s="1">
+      <c r="A120">
         <v>2267149</v>
       </c>
       <c r="B120" t="s">
@@ -6480,7 +6454,7 @@
       </c>
     </row>
     <row r="121" spans="1:16">
-      <c r="A121" s="1">
+      <c r="A121">
         <v>2267150</v>
       </c>
       <c r="B121" t="s">
@@ -6530,7 +6504,7 @@
       </c>
     </row>
     <row r="122" spans="1:16">
-      <c r="A122" s="1">
+      <c r="A122">
         <v>2267718</v>
       </c>
       <c r="B122" t="s">
@@ -6580,7 +6554,7 @@
       </c>
     </row>
     <row r="123" spans="1:16">
-      <c r="A123" s="1">
+      <c r="A123">
         <v>2267719</v>
       </c>
       <c r="B123" t="s">
@@ -6630,7 +6604,7 @@
       </c>
     </row>
     <row r="124" spans="1:16">
-      <c r="A124" s="1">
+      <c r="A124">
         <v>2267720</v>
       </c>
       <c r="B124" t="s">
@@ -6680,7 +6654,7 @@
       </c>
     </row>
     <row r="125" spans="1:16">
-      <c r="A125" s="1">
+      <c r="A125">
         <v>2267721</v>
       </c>
       <c r="B125" t="s">
@@ -6730,7 +6704,7 @@
       </c>
     </row>
     <row r="126" spans="1:16">
-      <c r="A126" s="1">
+      <c r="A126">
         <v>2267850</v>
       </c>
       <c r="B126" t="s">
@@ -6780,7 +6754,7 @@
       </c>
     </row>
     <row r="127" spans="1:16">
-      <c r="A127" s="1">
+      <c r="A127">
         <v>2267851</v>
       </c>
       <c r="B127" t="s">
@@ -6830,7 +6804,7 @@
       </c>
     </row>
     <row r="128" spans="1:16">
-      <c r="A128" s="1">
+      <c r="A128">
         <v>2268692</v>
       </c>
       <c r="B128" t="s">
@@ -6880,7 +6854,7 @@
       </c>
     </row>
     <row r="129" spans="1:16">
-      <c r="A129" s="1">
+      <c r="A129">
         <v>2268693</v>
       </c>
       <c r="B129" t="s">
@@ -6930,7 +6904,7 @@
       </c>
     </row>
     <row r="130" spans="1:16">
-      <c r="A130" s="1">
+      <c r="A130">
         <v>2268694</v>
       </c>
       <c r="B130" t="s">
@@ -6980,7 +6954,7 @@
       </c>
     </row>
     <row r="131" spans="1:16">
-      <c r="A131" s="1">
+      <c r="A131">
         <v>2268800</v>
       </c>
       <c r="B131" t="s">
@@ -7030,7 +7004,7 @@
       </c>
     </row>
     <row r="132" spans="1:16">
-      <c r="A132" s="1">
+      <c r="A132">
         <v>2268801</v>
       </c>
       <c r="B132" t="s">
@@ -7080,7 +7054,7 @@
       </c>
     </row>
     <row r="133" spans="1:16">
-      <c r="A133" s="1">
+      <c r="A133">
         <v>2268802</v>
       </c>
       <c r="B133" t="s">
@@ -7130,7 +7104,7 @@
       </c>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="1">
+      <c r="A134">
         <v>2268803</v>
       </c>
       <c r="B134" t="s">
@@ -7180,7 +7154,7 @@
       </c>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="1">
+      <c r="A135">
         <v>2269378</v>
       </c>
       <c r="B135" t="s">
@@ -7230,7 +7204,7 @@
       </c>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="1">
+      <c r="A136">
         <v>2269379</v>
       </c>
       <c r="B136" t="s">
@@ -7280,7 +7254,7 @@
       </c>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="1">
+      <c r="A137">
         <v>2269380</v>
       </c>
       <c r="B137" t="s">
@@ -7330,7 +7304,7 @@
       </c>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="1">
+      <c r="A138">
         <v>2270350</v>
       </c>
       <c r="B138" t="s">
@@ -7380,7 +7354,7 @@
       </c>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="1">
+      <c r="A139">
         <v>2270351</v>
       </c>
       <c r="B139" t="s">
@@ -7430,7 +7404,7 @@
       </c>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="1">
+      <c r="A140">
         <v>2270352</v>
       </c>
       <c r="B140" t="s">
@@ -7480,7 +7454,7 @@
       </c>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="1">
+      <c r="A141">
         <v>2270390</v>
       </c>
       <c r="B141" t="s">
@@ -7530,7 +7504,7 @@
       </c>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="1">
+      <c r="A142">
         <v>2270391</v>
       </c>
       <c r="B142" t="s">
@@ -7580,7 +7554,7 @@
       </c>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="1">
+      <c r="A143">
         <v>2270392</v>
       </c>
       <c r="B143" t="s">
@@ -7630,7 +7604,7 @@
       </c>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="1">
+      <c r="A144">
         <v>2271281</v>
       </c>
       <c r="B144" t="s">
@@ -7680,7 +7654,7 @@
       </c>
     </row>
     <row r="145" spans="1:16">
-      <c r="A145" s="1">
+      <c r="A145">
         <v>2271282</v>
       </c>
       <c r="B145" t="s">
@@ -7730,7 +7704,7 @@
       </c>
     </row>
     <row r="146" spans="1:16">
-      <c r="A146" s="1">
+      <c r="A146">
         <v>2271283</v>
       </c>
       <c r="B146" t="s">
@@ -7780,7 +7754,7 @@
       </c>
     </row>
     <row r="147" spans="1:16">
-      <c r="A147" s="1">
+      <c r="A147">
         <v>2271589</v>
       </c>
       <c r="B147" t="s">
@@ -7830,7 +7804,7 @@
       </c>
     </row>
     <row r="148" spans="1:16">
-      <c r="A148" s="1">
+      <c r="A148">
         <v>2271590</v>
       </c>
       <c r="B148" t="s">
@@ -7880,7 +7854,7 @@
       </c>
     </row>
     <row r="149" spans="1:16">
-      <c r="A149" s="1">
+      <c r="A149">
         <v>2271591</v>
       </c>
       <c r="B149" t="s">
@@ -7930,7 +7904,7 @@
       </c>
     </row>
     <row r="150" spans="1:16">
-      <c r="A150" s="1">
+      <c r="A150">
         <v>2272084</v>
       </c>
       <c r="B150" t="s">
@@ -7980,7 +7954,7 @@
       </c>
     </row>
     <row r="151" spans="1:16">
-      <c r="A151" s="1">
+      <c r="A151">
         <v>2272085</v>
       </c>
       <c r="B151" t="s">
@@ -8030,7 +8004,7 @@
       </c>
     </row>
     <row r="152" spans="1:16">
-      <c r="A152" s="1">
+      <c r="A152">
         <v>2272086</v>
       </c>
       <c r="B152" t="s">
@@ -8080,7 +8054,7 @@
       </c>
     </row>
     <row r="153" spans="1:16">
-      <c r="A153" s="1">
+      <c r="A153">
         <v>2272087</v>
       </c>
       <c r="B153" t="s">
@@ -8130,7 +8104,7 @@
       </c>
     </row>
     <row r="154" spans="1:16">
-      <c r="A154" s="1">
+      <c r="A154">
         <v>2301507</v>
       </c>
       <c r="B154" t="s">
@@ -8180,7 +8154,7 @@
       </c>
     </row>
     <row r="155" spans="1:16">
-      <c r="A155" s="1">
+      <c r="A155">
         <v>2301508</v>
       </c>
       <c r="B155" t="s">
@@ -8230,7 +8204,7 @@
       </c>
     </row>
     <row r="156" spans="1:16">
-      <c r="A156" s="1">
+      <c r="A156">
         <v>2301509</v>
       </c>
       <c r="B156" t="s">
@@ -8280,7 +8254,7 @@
       </c>
     </row>
     <row r="157" spans="1:16">
-      <c r="A157" s="1">
+      <c r="A157">
         <v>2301831</v>
       </c>
       <c r="B157" t="s">
@@ -8330,7 +8304,7 @@
       </c>
     </row>
     <row r="158" spans="1:16">
-      <c r="A158" s="1">
+      <c r="A158">
         <v>2301832</v>
       </c>
       <c r="B158" t="s">
@@ -8380,7 +8354,7 @@
       </c>
     </row>
     <row r="159" spans="1:16">
-      <c r="A159" s="1">
+      <c r="A159">
         <v>2301833</v>
       </c>
       <c r="B159" t="s">
@@ -8430,7 +8404,7 @@
       </c>
     </row>
     <row r="160" spans="1:16">
-      <c r="A160" s="1">
+      <c r="A160">
         <v>2305577</v>
       </c>
       <c r="B160" t="s">
@@ -8480,7 +8454,7 @@
       </c>
     </row>
     <row r="161" spans="1:16">
-      <c r="A161" s="1">
+      <c r="A161">
         <v>2305578</v>
       </c>
       <c r="B161" t="s">
@@ -8530,7 +8504,7 @@
       </c>
     </row>
     <row r="162" spans="1:16">
-      <c r="A162" s="1">
+      <c r="A162">
         <v>2305579</v>
       </c>
       <c r="B162" t="s">
@@ -8580,7 +8554,7 @@
       </c>
     </row>
     <row r="163" spans="1:16">
-      <c r="A163" s="1">
+      <c r="A163">
         <v>2305849</v>
       </c>
       <c r="B163" t="s">
@@ -8630,7 +8604,7 @@
       </c>
     </row>
     <row r="164" spans="1:16">
-      <c r="A164" s="1">
+      <c r="A164">
         <v>2305850</v>
       </c>
       <c r="B164" t="s">
@@ -8680,7 +8654,7 @@
       </c>
     </row>
     <row r="165" spans="1:16">
-      <c r="A165" s="1">
+      <c r="A165">
         <v>2305851</v>
       </c>
       <c r="B165" t="s">
@@ -8730,7 +8704,7 @@
       </c>
     </row>
     <row r="166" spans="1:16">
-      <c r="A166" s="1">
+      <c r="A166">
         <v>2306334</v>
       </c>
       <c r="B166" t="s">
@@ -8780,7 +8754,7 @@
       </c>
     </row>
     <row r="167" spans="1:16">
-      <c r="A167" s="1">
+      <c r="A167">
         <v>2306335</v>
       </c>
       <c r="B167" t="s">
@@ -8830,7 +8804,7 @@
       </c>
     </row>
     <row r="168" spans="1:16">
-      <c r="A168" s="1">
+      <c r="A168">
         <v>2306336</v>
       </c>
       <c r="B168" t="s">
@@ -8880,7 +8854,7 @@
       </c>
     </row>
     <row r="169" spans="1:16">
-      <c r="A169" s="1">
+      <c r="A169">
         <v>2308915</v>
       </c>
       <c r="B169" t="s">
@@ -8930,7 +8904,7 @@
       </c>
     </row>
     <row r="170" spans="1:16">
-      <c r="A170" s="1">
+      <c r="A170">
         <v>2308916</v>
       </c>
       <c r="B170" t="s">
@@ -8980,7 +8954,7 @@
       </c>
     </row>
     <row r="171" spans="1:16">
-      <c r="A171" s="1">
+      <c r="A171">
         <v>2308917</v>
       </c>
       <c r="B171" t="s">
@@ -9030,7 +9004,7 @@
       </c>
     </row>
     <row r="172" spans="1:16">
-      <c r="A172" s="1">
+      <c r="A172">
         <v>2309698</v>
       </c>
       <c r="B172" t="s">
@@ -9080,7 +9054,7 @@
       </c>
     </row>
     <row r="173" spans="1:16">
-      <c r="A173" s="1">
+      <c r="A173">
         <v>2309699</v>
       </c>
       <c r="B173" t="s">
@@ -9130,7 +9104,7 @@
       </c>
     </row>
     <row r="174" spans="1:16">
-      <c r="A174" s="1">
+      <c r="A174">
         <v>2309700</v>
       </c>
       <c r="B174" t="s">
@@ -9180,7 +9154,7 @@
       </c>
     </row>
     <row r="175" spans="1:16">
-      <c r="A175" s="1">
+      <c r="A175">
         <v>2310465</v>
       </c>
       <c r="B175" t="s">
@@ -9230,7 +9204,7 @@
       </c>
     </row>
     <row r="176" spans="1:16">
-      <c r="A176" s="1">
+      <c r="A176">
         <v>2310466</v>
       </c>
       <c r="B176" t="s">
@@ -9280,7 +9254,7 @@
       </c>
     </row>
     <row r="177" spans="1:16">
-      <c r="A177" s="1">
+      <c r="A177">
         <v>2310467</v>
       </c>
       <c r="B177" t="s">
@@ -9330,7 +9304,7 @@
       </c>
     </row>
     <row r="178" spans="1:16">
-      <c r="A178" s="1">
+      <c r="A178">
         <v>2312939</v>
       </c>
       <c r="B178" t="s">
@@ -9380,7 +9354,7 @@
       </c>
     </row>
     <row r="179" spans="1:16">
-      <c r="A179" s="1">
+      <c r="A179">
         <v>2312940</v>
       </c>
       <c r="B179" t="s">
@@ -9430,7 +9404,7 @@
       </c>
     </row>
     <row r="180" spans="1:16">
-      <c r="A180" s="1">
+      <c r="A180">
         <v>2312941</v>
       </c>
       <c r="B180" t="s">
@@ -9480,7 +9454,7 @@
       </c>
     </row>
     <row r="181" spans="1:16">
-      <c r="A181" s="1">
+      <c r="A181">
         <v>2312942</v>
       </c>
       <c r="B181" t="s">
@@ -9530,7 +9504,7 @@
       </c>
     </row>
     <row r="182" spans="1:16">
-      <c r="A182" s="1">
+      <c r="A182">
         <v>2313217</v>
       </c>
       <c r="B182" t="s">
@@ -9580,7 +9554,7 @@
       </c>
     </row>
     <row r="183" spans="1:16">
-      <c r="A183" s="1">
+      <c r="A183">
         <v>2313218</v>
       </c>
       <c r="B183" t="s">
@@ -9630,7 +9604,7 @@
       </c>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="1">
+      <c r="A184">
         <v>2313219</v>
       </c>
       <c r="B184" t="s">
@@ -9680,7 +9654,7 @@
       </c>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="1">
+      <c r="A185">
         <v>2314015</v>
       </c>
       <c r="B185" t="s">
@@ -9730,7 +9704,7 @@
       </c>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="1">
+      <c r="A186">
         <v>2314016</v>
       </c>
       <c r="B186" t="s">
@@ -9780,7 +9754,7 @@
       </c>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" s="1">
+      <c r="A187">
         <v>2314017</v>
       </c>
       <c r="B187" t="s">
@@ -9830,7 +9804,7 @@
       </c>
     </row>
     <row r="188" spans="1:16">
-      <c r="A188" s="1">
+      <c r="A188">
         <v>2314170</v>
       </c>
       <c r="B188" t="s">
@@ -9880,7 +9854,7 @@
       </c>
     </row>
     <row r="189" spans="1:16">
-      <c r="A189" s="1">
+      <c r="A189">
         <v>2314171</v>
       </c>
       <c r="B189" t="s">
@@ -9930,7 +9904,7 @@
       </c>
     </row>
     <row r="190" spans="1:16">
-      <c r="A190" s="1">
+      <c r="A190">
         <v>2314172</v>
       </c>
       <c r="B190" t="s">
@@ -9980,7 +9954,7 @@
       </c>
     </row>
     <row r="191" spans="1:16">
-      <c r="A191" s="1">
+      <c r="A191">
         <v>2396873</v>
       </c>
       <c r="B191" t="s">
@@ -10030,7 +10004,7 @@
       </c>
     </row>
     <row r="192" spans="1:16">
-      <c r="A192" s="1">
+      <c r="A192">
         <v>2396874</v>
       </c>
       <c r="B192" t="s">
@@ -10080,7 +10054,7 @@
       </c>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" s="1">
+      <c r="A193">
         <v>2396875</v>
       </c>
       <c r="B193" t="s">
@@ -10130,7 +10104,7 @@
       </c>
     </row>
     <row r="194" spans="1:16">
-      <c r="A194" s="1">
+      <c r="A194">
         <v>2396876</v>
       </c>
       <c r="B194" t="s">
@@ -10180,7 +10154,7 @@
       </c>
     </row>
     <row r="195" spans="1:16">
-      <c r="A195" s="1">
+      <c r="A195">
         <v>2397132</v>
       </c>
       <c r="B195" t="s">
@@ -10230,7 +10204,7 @@
       </c>
     </row>
     <row r="196" spans="1:16">
-      <c r="A196" s="1">
+      <c r="A196">
         <v>2397133</v>
       </c>
       <c r="B196" t="s">
@@ -10280,7 +10254,7 @@
       </c>
     </row>
     <row r="197" spans="1:16">
-      <c r="A197" s="1">
+      <c r="A197">
         <v>2397345</v>
       </c>
       <c r="B197" t="s">
@@ -10330,7 +10304,7 @@
       </c>
     </row>
     <row r="198" spans="1:16">
-      <c r="A198" s="1">
+      <c r="A198">
         <v>2397346</v>
       </c>
       <c r="B198" t="s">
@@ -10380,7 +10354,7 @@
       </c>
     </row>
     <row r="199" spans="1:16">
-      <c r="A199" s="1">
+      <c r="A199">
         <v>2397347</v>
       </c>
       <c r="B199" t="s">
@@ -10430,7 +10404,7 @@
       </c>
     </row>
     <row r="200" spans="1:16">
-      <c r="A200" s="1">
+      <c r="A200">
         <v>2397348</v>
       </c>
       <c r="B200" t="s">
@@ -10480,7 +10454,7 @@
       </c>
     </row>
     <row r="201" spans="1:16">
-      <c r="A201" s="1">
+      <c r="A201">
         <v>2397577</v>
       </c>
       <c r="B201" t="s">
@@ -10530,7 +10504,7 @@
       </c>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" s="1">
+      <c r="A202">
         <v>2397604</v>
       </c>
       <c r="B202" t="s">
@@ -10580,7 +10554,7 @@
       </c>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" s="1">
+      <c r="A203">
         <v>2397605</v>
       </c>
       <c r="B203" t="s">
@@ -10630,7 +10604,7 @@
       </c>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" s="1">
+      <c r="A204">
         <v>2397606</v>
       </c>
       <c r="B204" t="s">
@@ -10680,7 +10654,7 @@
       </c>
     </row>
     <row r="205" spans="1:16">
-      <c r="A205" s="1">
+      <c r="A205">
         <v>2397742</v>
       </c>
       <c r="B205" t="s">
@@ -10730,7 +10704,7 @@
       </c>
     </row>
     <row r="206" spans="1:16">
-      <c r="A206" s="1">
+      <c r="A206">
         <v>2397743</v>
       </c>
       <c r="B206" t="s">
@@ -10780,7 +10754,7 @@
       </c>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" s="1">
+      <c r="A207">
         <v>2397744</v>
       </c>
       <c r="B207" t="s">
@@ -10830,7 +10804,7 @@
       </c>
     </row>
     <row r="208" spans="1:16">
-      <c r="A208" s="1">
+      <c r="A208">
         <v>2397745</v>
       </c>
       <c r="B208" t="s">
@@ -10880,7 +10854,7 @@
       </c>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" s="1">
+      <c r="A209">
         <v>2398678</v>
       </c>
       <c r="B209" t="s">
@@ -10930,7 +10904,7 @@
       </c>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" s="1">
+      <c r="A210">
         <v>2398679</v>
       </c>
       <c r="B210" t="s">
@@ -10980,7 +10954,7 @@
       </c>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" s="1">
+      <c r="A211">
         <v>2398680</v>
       </c>
       <c r="B211" t="s">
@@ -11030,7 +11004,7 @@
       </c>
     </row>
     <row r="212" spans="1:16">
-      <c r="A212" s="1">
+      <c r="A212">
         <v>2398681</v>
       </c>
       <c r="B212" t="s">
@@ -11080,7 +11054,7 @@
       </c>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" s="1">
+      <c r="A213">
         <v>2398938</v>
       </c>
       <c r="B213" t="s">
@@ -11130,7 +11104,7 @@
       </c>
     </row>
     <row r="214" spans="1:16">
-      <c r="A214" s="1">
+      <c r="A214">
         <v>2398939</v>
       </c>
       <c r="B214" t="s">
@@ -11180,7 +11154,7 @@
       </c>
     </row>
     <row r="215" spans="1:16">
-      <c r="A215" s="1">
+      <c r="A215">
         <v>2398940</v>
       </c>
       <c r="B215" t="s">
@@ -11230,7 +11204,7 @@
       </c>
     </row>
     <row r="216" spans="1:16">
-      <c r="A216" s="1">
+      <c r="A216">
         <v>2398941</v>
       </c>
       <c r="B216" t="s">
@@ -11280,7 +11254,7 @@
       </c>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" s="1">
+      <c r="A217">
         <v>2399051</v>
       </c>
       <c r="B217" t="s">
@@ -11330,7 +11304,7 @@
       </c>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="1">
+      <c r="A218">
         <v>2399052</v>
       </c>
       <c r="B218" t="s">
@@ -11380,7 +11354,7 @@
       </c>
     </row>
     <row r="219" spans="1:16">
-      <c r="A219" s="1">
+      <c r="A219">
         <v>2399053</v>
       </c>
       <c r="B219" t="s">
@@ -11430,7 +11404,7 @@
       </c>
     </row>
     <row r="220" spans="1:16">
-      <c r="A220" s="1">
+      <c r="A220">
         <v>2399171</v>
       </c>
       <c r="B220" t="s">
@@ -11480,7 +11454,7 @@
       </c>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="1">
+      <c r="A221">
         <v>2399172</v>
       </c>
       <c r="B221" t="s">
@@ -11530,7 +11504,7 @@
       </c>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" s="1">
+      <c r="A222">
         <v>2399173</v>
       </c>
       <c r="B222" t="s">
@@ -11580,7 +11554,7 @@
       </c>
     </row>
     <row r="223" spans="1:16">
-      <c r="A223" s="1">
+      <c r="A223">
         <v>2399434</v>
       </c>
       <c r="B223" t="s">
@@ -11630,7 +11604,7 @@
       </c>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" s="1">
+      <c r="A224">
         <v>2399436</v>
       </c>
       <c r="B224" t="s">
@@ -11680,7 +11654,7 @@
       </c>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="1">
+      <c r="A225">
         <v>2399437</v>
       </c>
       <c r="B225" t="s">
@@ -11730,7 +11704,7 @@
       </c>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="1">
+      <c r="A226">
         <v>2399467</v>
       </c>
       <c r="B226" t="s">
@@ -11780,7 +11754,7 @@
       </c>
     </row>
     <row r="227" spans="1:16">
-      <c r="A227" s="1">
+      <c r="A227">
         <v>2399468</v>
       </c>
       <c r="B227" t="s">
@@ -11830,7 +11804,7 @@
       </c>
     </row>
     <row r="228" spans="1:16">
-      <c r="A228" s="1">
+      <c r="A228">
         <v>2399469</v>
       </c>
       <c r="B228" t="s">
@@ -11880,7 +11854,7 @@
       </c>
     </row>
     <row r="229" spans="1:16">
-      <c r="A229" s="1">
+      <c r="A229">
         <v>2399470</v>
       </c>
       <c r="B229" t="s">
@@ -11930,7 +11904,7 @@
       </c>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" s="1">
+      <c r="A230">
         <v>2399615</v>
       </c>
       <c r="B230" t="s">
@@ -11980,7 +11954,7 @@
       </c>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="1">
+      <c r="A231">
         <v>2399616</v>
       </c>
       <c r="B231" t="s">
@@ -12030,7 +12004,7 @@
       </c>
     </row>
     <row r="232" spans="1:16">
-      <c r="A232" s="1">
+      <c r="A232">
         <v>2399617</v>
       </c>
       <c r="B232" t="s">
@@ -12080,7 +12054,7 @@
       </c>
     </row>
     <row r="233" spans="1:16">
-      <c r="A233" s="1">
+      <c r="A233">
         <v>2457745</v>
       </c>
       <c r="B233" t="s">
@@ -12130,7 +12104,7 @@
       </c>
     </row>
     <row r="234" spans="1:16">
-      <c r="A234" s="1">
+      <c r="A234">
         <v>2457746</v>
       </c>
       <c r="B234" t="s">
@@ -12180,7 +12154,7 @@
       </c>
     </row>
     <row r="235" spans="1:16">
-      <c r="A235" s="1">
+      <c r="A235">
         <v>2457747</v>
       </c>
       <c r="B235" t="s">
@@ -12230,7 +12204,7 @@
       </c>
     </row>
     <row r="236" spans="1:16">
-      <c r="A236" s="1">
+      <c r="A236">
         <v>2457984</v>
       </c>
       <c r="B236" t="s">
@@ -12277,7 +12251,7 @@
       </c>
     </row>
     <row r="237" spans="1:16">
-      <c r="A237" s="1">
+      <c r="A237">
         <v>2457985</v>
       </c>
       <c r="B237" t="s">
@@ -12324,7 +12298,7 @@
       </c>
     </row>
     <row r="238" spans="1:16">
-      <c r="A238" s="1">
+      <c r="A238">
         <v>2457986</v>
       </c>
       <c r="B238" t="s">
@@ -12374,7 +12348,7 @@
       </c>
     </row>
     <row r="239" spans="1:16">
-      <c r="A239" s="1">
+      <c r="A239">
         <v>2458188</v>
       </c>
       <c r="B239" t="s">
@@ -12424,7 +12398,7 @@
       </c>
     </row>
     <row r="240" spans="1:16">
-      <c r="A240" s="1">
+      <c r="A240">
         <v>2458189</v>
       </c>
       <c r="B240" t="s">
@@ -12474,7 +12448,7 @@
       </c>
     </row>
     <row r="241" spans="1:16">
-      <c r="A241" s="1">
+      <c r="A241">
         <v>2458190</v>
       </c>
       <c r="B241" t="s">
@@ -12524,7 +12498,7 @@
       </c>
     </row>
     <row r="242" spans="1:16">
-      <c r="A242" s="1">
+      <c r="A242">
         <v>2458430</v>
       </c>
       <c r="B242" t="s">
@@ -12571,7 +12545,7 @@
       </c>
     </row>
     <row r="243" spans="1:16">
-      <c r="A243" s="1">
+      <c r="A243">
         <v>2458431</v>
       </c>
       <c r="B243" t="s">
@@ -12618,7 +12592,7 @@
       </c>
     </row>
     <row r="244" spans="1:16">
-      <c r="A244" s="1">
+      <c r="A244">
         <v>2458432</v>
       </c>
       <c r="B244" t="s">
@@ -12665,7 +12639,7 @@
       </c>
     </row>
     <row r="245" spans="1:16">
-      <c r="A245" s="1">
+      <c r="A245">
         <v>2458490</v>
       </c>
       <c r="B245" t="s">
@@ -12712,7 +12686,7 @@
       </c>
     </row>
     <row r="246" spans="1:16">
-      <c r="A246" s="1">
+      <c r="A246">
         <v>2458491</v>
       </c>
       <c r="B246" t="s">
@@ -12759,7 +12733,7 @@
       </c>
     </row>
     <row r="247" spans="1:16">
-      <c r="A247" s="1">
+      <c r="A247">
         <v>2458492</v>
       </c>
       <c r="B247" t="s">
@@ -12809,7 +12783,7 @@
       </c>
     </row>
     <row r="248" spans="1:16">
-      <c r="A248" s="1">
+      <c r="A248">
         <v>2458576</v>
       </c>
       <c r="B248" t="s">
@@ -12859,7 +12833,7 @@
       </c>
     </row>
     <row r="249" spans="1:16">
-      <c r="A249" s="1">
+      <c r="A249">
         <v>2458626</v>
       </c>
       <c r="B249" t="s">
@@ -12909,7 +12883,7 @@
       </c>
     </row>
     <row r="250" spans="1:16">
-      <c r="A250" s="1">
+      <c r="A250">
         <v>2458627</v>
       </c>
       <c r="B250" t="s">
@@ -12959,7 +12933,7 @@
       </c>
     </row>
     <row r="251" spans="1:16">
-      <c r="A251" s="1">
+      <c r="A251">
         <v>2458628</v>
       </c>
       <c r="B251" t="s">
@@ -13009,7 +12983,7 @@
       </c>
     </row>
     <row r="252" spans="1:16">
-      <c r="A252" s="1">
+      <c r="A252">
         <v>2458646</v>
       </c>
       <c r="B252" t="s">
@@ -13059,7 +13033,7 @@
       </c>
     </row>
     <row r="253" spans="1:16">
-      <c r="A253" s="1">
+      <c r="A253">
         <v>2458647</v>
       </c>
       <c r="B253" t="s">
@@ -13109,7 +13083,7 @@
       </c>
     </row>
     <row r="254" spans="1:16">
-      <c r="A254" s="1">
+      <c r="A254">
         <v>2458761</v>
       </c>
       <c r="B254" t="s">
@@ -13159,7 +13133,7 @@
       </c>
     </row>
     <row r="255" spans="1:16">
-      <c r="A255" s="1">
+      <c r="A255">
         <v>2458762</v>
       </c>
       <c r="B255" t="s">
@@ -13209,7 +13183,7 @@
       </c>
     </row>
     <row r="256" spans="1:16">
-      <c r="A256" s="1">
+      <c r="A256">
         <v>2458763</v>
       </c>
       <c r="B256" t="s">
@@ -13259,7 +13233,7 @@
       </c>
     </row>
     <row r="257" spans="1:16">
-      <c r="A257" s="1">
+      <c r="A257">
         <v>2458764</v>
       </c>
       <c r="B257" t="s">
@@ -13309,7 +13283,7 @@
       </c>
     </row>
     <row r="258" spans="1:16">
-      <c r="A258" s="1">
+      <c r="A258">
         <v>2459656</v>
       </c>
       <c r="B258" t="s">
@@ -13359,7 +13333,7 @@
       </c>
     </row>
     <row r="259" spans="1:16">
-      <c r="A259" s="1">
+      <c r="A259">
         <v>2459657</v>
       </c>
       <c r="B259" t="s">
@@ -13409,7 +13383,7 @@
       </c>
     </row>
     <row r="260" spans="1:16">
-      <c r="A260" s="1">
+      <c r="A260">
         <v>2459658</v>
       </c>
       <c r="B260" t="s">
@@ -13459,7 +13433,7 @@
       </c>
     </row>
     <row r="261" spans="1:16">
-      <c r="A261" s="1">
+      <c r="A261">
         <v>2459958</v>
       </c>
       <c r="B261" t="s">
@@ -13509,7 +13483,7 @@
       </c>
     </row>
     <row r="262" spans="1:16">
-      <c r="A262" s="1">
+      <c r="A262">
         <v>2459959</v>
       </c>
       <c r="B262" t="s">
@@ -13559,7 +13533,7 @@
       </c>
     </row>
     <row r="263" spans="1:16">
-      <c r="A263" s="1">
+      <c r="A263">
         <v>2459960</v>
       </c>
       <c r="B263" t="s">
@@ -13609,7 +13583,7 @@
       </c>
     </row>
     <row r="264" spans="1:16">
-      <c r="A264" s="1">
+      <c r="A264">
         <v>2460177</v>
       </c>
       <c r="B264" t="s">
@@ -13659,7 +13633,7 @@
       </c>
     </row>
     <row r="265" spans="1:16">
-      <c r="A265" s="1">
+      <c r="A265">
         <v>2460178</v>
       </c>
       <c r="B265" t="s">
@@ -13709,7 +13683,7 @@
       </c>
     </row>
     <row r="266" spans="1:16">
-      <c r="A266" s="1">
+      <c r="A266">
         <v>2460179</v>
       </c>
       <c r="B266" t="s">
@@ -13759,7 +13733,7 @@
       </c>
     </row>
     <row r="267" spans="1:16">
-      <c r="A267" s="1">
+      <c r="A267">
         <v>2460180</v>
       </c>
       <c r="B267" t="s">
@@ -13809,7 +13783,7 @@
       </c>
     </row>
     <row r="268" spans="1:16">
-      <c r="A268" s="1">
+      <c r="A268">
         <v>2460723</v>
       </c>
       <c r="B268" t="s">
@@ -13859,7 +13833,7 @@
       </c>
     </row>
     <row r="269" spans="1:16">
-      <c r="A269" s="1">
+      <c r="A269">
         <v>2460724</v>
       </c>
       <c r="B269" t="s">
@@ -13909,7 +13883,7 @@
       </c>
     </row>
     <row r="270" spans="1:16">
-      <c r="A270" s="1">
+      <c r="A270">
         <v>2460725</v>
       </c>
       <c r="B270" t="s">
@@ -13959,7 +13933,7 @@
       </c>
     </row>
     <row r="271" spans="1:16">
-      <c r="A271" s="1">
+      <c r="A271">
         <v>2889323</v>
       </c>
       <c r="B271" t="s">
@@ -14009,7 +13983,7 @@
       </c>
     </row>
     <row r="272" spans="1:16">
-      <c r="A272" s="1">
+      <c r="A272">
         <v>2889324</v>
       </c>
       <c r="B272" t="s">
@@ -14059,7 +14033,7 @@
       </c>
     </row>
     <row r="273" spans="1:16">
-      <c r="A273" s="1">
+      <c r="A273">
         <v>2889325</v>
       </c>
       <c r="B273" t="s">
@@ -14109,7 +14083,7 @@
       </c>
     </row>
     <row r="274" spans="1:16">
-      <c r="A274" s="1">
+      <c r="A274">
         <v>2889326</v>
       </c>
       <c r="B274" t="s">
@@ -14159,7 +14133,7 @@
       </c>
     </row>
     <row r="275" spans="1:16">
-      <c r="A275" s="1">
+      <c r="A275">
         <v>2889327</v>
       </c>
       <c r="B275" t="s">
@@ -14209,7 +14183,7 @@
       </c>
     </row>
     <row r="276" spans="1:16">
-      <c r="A276" s="1">
+      <c r="A276">
         <v>2889817</v>
       </c>
       <c r="B276" t="s">
@@ -14259,7 +14233,7 @@
       </c>
     </row>
     <row r="277" spans="1:16">
-      <c r="A277" s="1">
+      <c r="A277">
         <v>2889818</v>
       </c>
       <c r="B277" t="s">
@@ -14309,7 +14283,7 @@
       </c>
     </row>
     <row r="278" spans="1:16">
-      <c r="A278" s="1">
+      <c r="A278">
         <v>2889819</v>
       </c>
       <c r="B278" t="s">
@@ -14359,7 +14333,7 @@
       </c>
     </row>
     <row r="279" spans="1:16">
-      <c r="A279" s="1">
+      <c r="A279">
         <v>2889820</v>
       </c>
       <c r="B279" t="s">
@@ -14409,7 +14383,7 @@
       </c>
     </row>
     <row r="280" spans="1:16">
-      <c r="A280" s="1">
+      <c r="A280">
         <v>2889821</v>
       </c>
       <c r="B280" t="s">
@@ -14459,7 +14433,7 @@
       </c>
     </row>
     <row r="281" spans="1:16">
-      <c r="A281" s="1">
+      <c r="A281">
         <v>2890490</v>
       </c>
       <c r="B281" t="s">
@@ -14509,7 +14483,7 @@
       </c>
     </row>
     <row r="282" spans="1:16">
-      <c r="A282" s="1">
+      <c r="A282">
         <v>2890491</v>
       </c>
       <c r="B282" t="s">
@@ -14559,7 +14533,7 @@
       </c>
     </row>
     <row r="283" spans="1:16">
-      <c r="A283" s="1">
+      <c r="A283">
         <v>2890492</v>
       </c>
       <c r="B283" t="s">
@@ -14609,7 +14583,7 @@
       </c>
     </row>
     <row r="284" spans="1:16">
-      <c r="A284" s="1">
+      <c r="A284">
         <v>2890493</v>
       </c>
       <c r="B284" t="s">
@@ -14659,7 +14633,7 @@
       </c>
     </row>
     <row r="285" spans="1:16">
-      <c r="A285" s="1">
+      <c r="A285">
         <v>2890494</v>
       </c>
       <c r="B285" t="s">
@@ -14709,7 +14683,7 @@
       </c>
     </row>
     <row r="286" spans="1:16">
-      <c r="A286" s="1">
+      <c r="A286">
         <v>2890618</v>
       </c>
       <c r="B286" t="s">
@@ -14759,7 +14733,7 @@
       </c>
     </row>
     <row r="287" spans="1:16">
-      <c r="A287" s="1">
+      <c r="A287">
         <v>2890619</v>
       </c>
       <c r="B287" t="s">
@@ -14809,7 +14783,7 @@
       </c>
     </row>
     <row r="288" spans="1:16">
-      <c r="A288" s="1">
+      <c r="A288">
         <v>2890662</v>
       </c>
       <c r="B288" t="s">
@@ -14859,7 +14833,7 @@
       </c>
     </row>
     <row r="289" spans="1:16">
-      <c r="A289" s="1">
+      <c r="A289">
         <v>2890663</v>
       </c>
       <c r="B289" t="s">
@@ -14909,7 +14883,7 @@
       </c>
     </row>
     <row r="290" spans="1:16">
-      <c r="A290" s="1">
+      <c r="A290">
         <v>2892978</v>
       </c>
       <c r="B290" t="s">
@@ -14959,7 +14933,7 @@
       </c>
     </row>
     <row r="291" spans="1:16">
-      <c r="A291" s="1">
+      <c r="A291">
         <v>2892979</v>
       </c>
       <c r="B291" t="s">
@@ -15009,7 +14983,7 @@
       </c>
     </row>
     <row r="292" spans="1:16">
-      <c r="A292" s="1">
+      <c r="A292">
         <v>2892980</v>
       </c>
       <c r="B292" t="s">
@@ -15059,7 +15033,7 @@
       </c>
     </row>
     <row r="293" spans="1:16">
-      <c r="A293" s="1">
+      <c r="A293">
         <v>2892981</v>
       </c>
       <c r="B293" t="s">
@@ -15109,7 +15083,7 @@
       </c>
     </row>
     <row r="294" spans="1:16">
-      <c r="A294" s="1">
+      <c r="A294">
         <v>2894076</v>
       </c>
       <c r="B294" t="s">
@@ -15159,7 +15133,7 @@
       </c>
     </row>
     <row r="295" spans="1:16">
-      <c r="A295" s="1">
+      <c r="A295">
         <v>2894077</v>
       </c>
       <c r="B295" t="s">
@@ -15209,7 +15183,7 @@
       </c>
     </row>
     <row r="296" spans="1:16">
-      <c r="A296" s="1">
+      <c r="A296">
         <v>2894078</v>
       </c>
       <c r="B296" t="s">
@@ -15259,7 +15233,7 @@
       </c>
     </row>
     <row r="297" spans="1:16">
-      <c r="A297" s="1">
+      <c r="A297">
         <v>2894079</v>
       </c>
       <c r="B297" t="s">
@@ -15309,7 +15283,7 @@
       </c>
     </row>
     <row r="298" spans="1:16">
-      <c r="A298" s="1">
+      <c r="A298">
         <v>2894080</v>
       </c>
       <c r="B298" t="s">
@@ -15359,7 +15333,7 @@
       </c>
     </row>
     <row r="299" spans="1:16">
-      <c r="A299" s="1">
+      <c r="A299">
         <v>2895414</v>
       </c>
       <c r="B299" t="s">
@@ -15409,7 +15383,7 @@
       </c>
     </row>
     <row r="300" spans="1:16">
-      <c r="A300" s="1">
+      <c r="A300">
         <v>2895415</v>
       </c>
       <c r="B300" t="s">
@@ -15459,7 +15433,7 @@
       </c>
     </row>
     <row r="301" spans="1:16">
-      <c r="A301" s="1">
+      <c r="A301">
         <v>2895416</v>
       </c>
       <c r="B301" t="s">
@@ -15509,7 +15483,7 @@
       </c>
     </row>
     <row r="302" spans="1:16">
-      <c r="A302" s="1">
+      <c r="A302">
         <v>2895417</v>
       </c>
       <c r="B302" t="s">
@@ -15559,7 +15533,7 @@
       </c>
     </row>
     <row r="303" spans="1:16">
-      <c r="A303" s="1">
+      <c r="A303">
         <v>2895418</v>
       </c>
       <c r="B303" t="s">
@@ -15609,7 +15583,7 @@
       </c>
     </row>
     <row r="304" spans="1:16">
-      <c r="A304" s="1">
+      <c r="A304">
         <v>2895419</v>
       </c>
       <c r="B304" t="s">
@@ -15659,7 +15633,7 @@
       </c>
     </row>
     <row r="305" spans="1:16">
-      <c r="A305" s="1">
+      <c r="A305">
         <v>2898531</v>
       </c>
       <c r="B305" t="s">
@@ -15709,7 +15683,7 @@
       </c>
     </row>
     <row r="306" spans="1:16">
-      <c r="A306" s="1">
+      <c r="A306">
         <v>2898532</v>
       </c>
       <c r="B306" t="s">
@@ -15759,7 +15733,7 @@
       </c>
     </row>
     <row r="307" spans="1:16">
-      <c r="A307" s="1">
+      <c r="A307">
         <v>2898533</v>
       </c>
       <c r="B307" t="s">
@@ -15809,7 +15783,7 @@
       </c>
     </row>
     <row r="308" spans="1:16">
-      <c r="A308" s="1">
+      <c r="A308">
         <v>2898534</v>
       </c>
       <c r="B308" t="s">
@@ -15859,7 +15833,7 @@
       </c>
     </row>
     <row r="309" spans="1:16">
-      <c r="A309" s="1">
+      <c r="A309">
         <v>2900126</v>
       </c>
       <c r="B309" t="s">
@@ -15909,7 +15883,7 @@
       </c>
     </row>
     <row r="310" spans="1:16">
-      <c r="A310" s="1">
+      <c r="A310">
         <v>2900127</v>
       </c>
       <c r="B310" t="s">
@@ -15959,7 +15933,7 @@
       </c>
     </row>
     <row r="311" spans="1:16">
-      <c r="A311" s="1">
+      <c r="A311">
         <v>2900128</v>
       </c>
       <c r="B311" t="s">
@@ -16009,7 +15983,7 @@
       </c>
     </row>
     <row r="312" spans="1:16">
-      <c r="A312" s="1">
+      <c r="A312">
         <v>2900129</v>
       </c>
       <c r="B312" t="s">
@@ -16059,7 +16033,7 @@
       </c>
     </row>
     <row r="313" spans="1:16">
-      <c r="A313" s="1">
+      <c r="A313">
         <v>2900130</v>
       </c>
       <c r="B313" t="s">
@@ -16109,7 +16083,7 @@
       </c>
     </row>
     <row r="314" spans="1:16">
-      <c r="A314" s="1">
+      <c r="A314">
         <v>2901264</v>
       </c>
       <c r="B314" t="s">
@@ -16159,7 +16133,7 @@
       </c>
     </row>
     <row r="315" spans="1:16">
-      <c r="A315" s="1">
+      <c r="A315">
         <v>2901265</v>
       </c>
       <c r="B315" t="s">
@@ -16209,7 +16183,7 @@
       </c>
     </row>
     <row r="316" spans="1:16">
-      <c r="A316" s="1">
+      <c r="A316">
         <v>2901266</v>
       </c>
       <c r="B316" t="s">
@@ -16259,7 +16233,7 @@
       </c>
     </row>
     <row r="317" spans="1:16">
-      <c r="A317" s="1">
+      <c r="A317">
         <v>2901267</v>
       </c>
       <c r="B317" t="s">
@@ -16309,7 +16283,7 @@
       </c>
     </row>
     <row r="318" spans="1:16">
-      <c r="A318" s="1">
+      <c r="A318">
         <v>2901268</v>
       </c>
       <c r="B318" t="s">
@@ -16359,7 +16333,7 @@
       </c>
     </row>
     <row r="319" spans="1:16">
-      <c r="A319" s="1">
+      <c r="A319">
         <v>2902109</v>
       </c>
       <c r="B319" t="s">
@@ -16409,7 +16383,7 @@
       </c>
     </row>
     <row r="320" spans="1:16">
-      <c r="A320" s="1">
+      <c r="A320">
         <v>2902110</v>
       </c>
       <c r="B320" t="s">
@@ -16459,7 +16433,7 @@
       </c>
     </row>
     <row r="321" spans="1:16">
-      <c r="A321" s="1">
+      <c r="A321">
         <v>2902111</v>
       </c>
       <c r="B321" t="s">
@@ -16509,7 +16483,7 @@
       </c>
     </row>
     <row r="322" spans="1:16">
-      <c r="A322" s="1">
+      <c r="A322">
         <v>2902112</v>
       </c>
       <c r="B322" t="s">
@@ -16559,7 +16533,7 @@
       </c>
     </row>
     <row r="323" spans="1:16">
-      <c r="A323" s="1">
+      <c r="A323">
         <v>2902113</v>
       </c>
       <c r="B323" t="s">
@@ -16609,7 +16583,7 @@
       </c>
     </row>
     <row r="324" spans="1:16">
-      <c r="A324" s="1">
+      <c r="A324">
         <v>2902493</v>
       </c>
       <c r="B324" t="s">
@@ -16659,7 +16633,7 @@
       </c>
     </row>
     <row r="325" spans="1:16">
-      <c r="A325" s="1">
+      <c r="A325">
         <v>2902494</v>
       </c>
       <c r="B325" t="s">
@@ -16709,7 +16683,7 @@
       </c>
     </row>
     <row r="326" spans="1:16">
-      <c r="A326" s="1">
+      <c r="A326">
         <v>2902495</v>
       </c>
       <c r="B326" t="s">
@@ -16759,7 +16733,7 @@
       </c>
     </row>
     <row r="327" spans="1:16">
-      <c r="A327" s="1">
+      <c r="A327">
         <v>2902496</v>
       </c>
       <c r="B327" t="s">
@@ -16809,7 +16783,7 @@
       </c>
     </row>
     <row r="328" spans="1:16">
-      <c r="A328" s="1">
+      <c r="A328">
         <v>2902497</v>
       </c>
       <c r="B328" t="s">
@@ -16859,7 +16833,7 @@
       </c>
     </row>
     <row r="329" spans="1:16">
-      <c r="A329" s="1">
+      <c r="A329">
         <v>2946810</v>
       </c>
       <c r="B329" t="s">
@@ -16909,7 +16883,7 @@
       </c>
     </row>
     <row r="330" spans="1:16">
-      <c r="A330" s="1">
+      <c r="A330">
         <v>2946811</v>
       </c>
       <c r="B330" t="s">
@@ -16959,7 +16933,7 @@
       </c>
     </row>
     <row r="331" spans="1:16">
-      <c r="A331" s="1">
+      <c r="A331">
         <v>2946812</v>
       </c>
       <c r="B331" t="s">
@@ -17009,7 +16983,7 @@
       </c>
     </row>
     <row r="332" spans="1:16">
-      <c r="A332" s="1">
+      <c r="A332">
         <v>2946813</v>
       </c>
       <c r="B332" t="s">
@@ -17059,7 +17033,7 @@
       </c>
     </row>
     <row r="333" spans="1:16">
-      <c r="A333" s="1">
+      <c r="A333">
         <v>2947150</v>
       </c>
       <c r="B333" t="s">
@@ -17109,7 +17083,7 @@
       </c>
     </row>
     <row r="334" spans="1:16">
-      <c r="A334" s="1">
+      <c r="A334">
         <v>2947151</v>
       </c>
       <c r="B334" t="s">
@@ -17159,7 +17133,7 @@
       </c>
     </row>
     <row r="335" spans="1:16">
-      <c r="A335" s="1">
+      <c r="A335">
         <v>2947152</v>
       </c>
       <c r="B335" t="s">
@@ -17209,7 +17183,7 @@
       </c>
     </row>
     <row r="336" spans="1:16">
-      <c r="A336" s="1">
+      <c r="A336">
         <v>2947277</v>
       </c>
       <c r="B336" t="s">
@@ -17259,7 +17233,7 @@
       </c>
     </row>
     <row r="337" spans="1:16">
-      <c r="A337" s="1">
+      <c r="A337">
         <v>2947278</v>
       </c>
       <c r="B337" t="s">
@@ -17309,7 +17283,7 @@
       </c>
     </row>
     <row r="338" spans="1:16">
-      <c r="A338" s="1">
+      <c r="A338">
         <v>2947279</v>
       </c>
       <c r="B338" t="s">
@@ -17359,7 +17333,7 @@
       </c>
     </row>
     <row r="339" spans="1:16">
-      <c r="A339" s="1">
+      <c r="A339">
         <v>2947564</v>
       </c>
       <c r="B339" t="s">
@@ -17409,7 +17383,7 @@
       </c>
     </row>
     <row r="340" spans="1:16">
-      <c r="A340" s="1">
+      <c r="A340">
         <v>2947565</v>
       </c>
       <c r="B340" t="s">
@@ -17459,7 +17433,7 @@
       </c>
     </row>
     <row r="341" spans="1:16">
-      <c r="A341" s="1">
+      <c r="A341">
         <v>2947566</v>
       </c>
       <c r="B341" t="s">
@@ -17509,7 +17483,7 @@
       </c>
     </row>
     <row r="342" spans="1:16">
-      <c r="A342" s="1">
+      <c r="A342">
         <v>2947567</v>
       </c>
       <c r="B342" t="s">
@@ -17559,7 +17533,7 @@
       </c>
     </row>
     <row r="343" spans="1:16">
-      <c r="A343" s="1">
+      <c r="A343">
         <v>2947690</v>
       </c>
       <c r="B343" t="s">
@@ -17609,7 +17583,7 @@
       </c>
     </row>
     <row r="344" spans="1:16">
-      <c r="A344" s="1">
+      <c r="A344">
         <v>2947691</v>
       </c>
       <c r="B344" t="s">
@@ -17659,7 +17633,7 @@
       </c>
     </row>
     <row r="345" spans="1:16">
-      <c r="A345" s="1">
+      <c r="A345">
         <v>2947692</v>
       </c>
       <c r="B345" t="s">
@@ -17709,7 +17683,7 @@
       </c>
     </row>
     <row r="346" spans="1:16">
-      <c r="A346" s="1">
+      <c r="A346">
         <v>2947777</v>
       </c>
       <c r="B346" t="s">
@@ -17759,7 +17733,7 @@
       </c>
     </row>
     <row r="347" spans="1:16">
-      <c r="A347" s="1">
+      <c r="A347">
         <v>2947778</v>
       </c>
       <c r="B347" t="s">
@@ -17809,7 +17783,7 @@
       </c>
     </row>
     <row r="348" spans="1:16">
-      <c r="A348" s="1">
+      <c r="A348">
         <v>2947779</v>
       </c>
       <c r="B348" t="s">
@@ -17859,7 +17833,7 @@
       </c>
     </row>
     <row r="349" spans="1:16">
-      <c r="A349" s="1">
+      <c r="A349">
         <v>2947780</v>
       </c>
       <c r="B349" t="s">
@@ -17909,7 +17883,7 @@
       </c>
     </row>
     <row r="350" spans="1:16">
-      <c r="A350" s="1">
+      <c r="A350">
         <v>2948176</v>
       </c>
       <c r="B350" t="s">
@@ -17959,7 +17933,7 @@
       </c>
     </row>
     <row r="351" spans="1:16">
-      <c r="A351" s="1">
+      <c r="A351">
         <v>2948177</v>
       </c>
       <c r="B351" t="s">
@@ -18009,7 +17983,7 @@
       </c>
     </row>
     <row r="352" spans="1:16">
-      <c r="A352" s="1">
+      <c r="A352">
         <v>2948178</v>
       </c>
       <c r="B352" t="s">
@@ -18059,7 +18033,7 @@
       </c>
     </row>
     <row r="353" spans="1:16">
-      <c r="A353" s="1">
+      <c r="A353">
         <v>2948179</v>
       </c>
       <c r="B353" t="s">
@@ -18109,7 +18083,7 @@
       </c>
     </row>
     <row r="354" spans="1:16">
-      <c r="A354" s="1">
+      <c r="A354">
         <v>2948180</v>
       </c>
       <c r="B354" t="s">
@@ -18159,7 +18133,7 @@
       </c>
     </row>
     <row r="355" spans="1:16">
-      <c r="A355" s="1">
+      <c r="A355">
         <v>2948327</v>
       </c>
       <c r="B355" t="s">
@@ -18209,7 +18183,7 @@
       </c>
     </row>
     <row r="356" spans="1:16">
-      <c r="A356" s="1">
+      <c r="A356">
         <v>2948328</v>
       </c>
       <c r="B356" t="s">
@@ -18259,7 +18233,7 @@
       </c>
     </row>
     <row r="357" spans="1:16">
-      <c r="A357" s="1">
+      <c r="A357">
         <v>2948329</v>
       </c>
       <c r="B357" t="s">
@@ -18309,7 +18283,7 @@
       </c>
     </row>
     <row r="358" spans="1:16">
-      <c r="A358" s="1">
+      <c r="A358">
         <v>2948626</v>
       </c>
       <c r="B358" t="s">
@@ -18359,7 +18333,7 @@
       </c>
     </row>
     <row r="359" spans="1:16">
-      <c r="A359" s="1">
+      <c r="A359">
         <v>2948627</v>
       </c>
       <c r="B359" t="s">
@@ -18409,7 +18383,7 @@
       </c>
     </row>
     <row r="360" spans="1:16">
-      <c r="A360" s="1">
+      <c r="A360">
         <v>2948628</v>
       </c>
       <c r="B360" t="s">
@@ -18459,7 +18433,7 @@
       </c>
     </row>
     <row r="361" spans="1:16">
-      <c r="A361" s="1">
+      <c r="A361">
         <v>2948629</v>
       </c>
       <c r="B361" t="s">
@@ -18509,7 +18483,7 @@
       </c>
     </row>
     <row r="362" spans="1:16">
-      <c r="A362" s="1">
+      <c r="A362">
         <v>2949300</v>
       </c>
       <c r="B362" t="s">
@@ -18559,7 +18533,7 @@
       </c>
     </row>
     <row r="363" spans="1:16">
-      <c r="A363" s="1">
+      <c r="A363">
         <v>2949301</v>
       </c>
       <c r="B363" t="s">
@@ -18609,7 +18583,7 @@
       </c>
     </row>
     <row r="364" spans="1:16">
-      <c r="A364" s="1">
+      <c r="A364">
         <v>2949302</v>
       </c>
       <c r="B364" t="s">
@@ -18659,7 +18633,7 @@
       </c>
     </row>
     <row r="365" spans="1:16">
-      <c r="A365" s="1">
+      <c r="A365">
         <v>2949486</v>
       </c>
       <c r="B365" t="s">
@@ -18709,7 +18683,7 @@
       </c>
     </row>
     <row r="366" spans="1:16">
-      <c r="A366" s="1">
+      <c r="A366">
         <v>2949487</v>
       </c>
       <c r="B366" t="s">
@@ -18759,7 +18733,7 @@
       </c>
     </row>
     <row r="367" spans="1:16">
-      <c r="A367" s="1">
+      <c r="A367">
         <v>2949488</v>
       </c>
       <c r="B367" t="s">
@@ -18809,7 +18783,7 @@
       </c>
     </row>
     <row r="368" spans="1:16">
-      <c r="A368" s="1">
+      <c r="A368">
         <v>2949729</v>
       </c>
       <c r="B368" t="s">
@@ -18859,7 +18833,7 @@
       </c>
     </row>
     <row r="369" spans="1:16">
-      <c r="A369" s="1">
+      <c r="A369">
         <v>2949730</v>
       </c>
       <c r="B369" t="s">
@@ -18909,7 +18883,7 @@
       </c>
     </row>
     <row r="370" spans="1:16">
-      <c r="A370" s="1">
+      <c r="A370">
         <v>2949731</v>
       </c>
       <c r="B370" t="s">
@@ -18959,7 +18933,7 @@
       </c>
     </row>
     <row r="371" spans="1:16">
-      <c r="A371" s="1">
+      <c r="A371">
         <v>2949732</v>
       </c>
       <c r="B371" t="s">
@@ -19009,7 +18983,7 @@
       </c>
     </row>
     <row r="372" spans="1:16">
-      <c r="A372" s="1">
+      <c r="A372">
         <v>2954770</v>
       </c>
       <c r="B372" t="s">
@@ -19059,7 +19033,7 @@
       </c>
     </row>
     <row r="373" spans="1:16">
-      <c r="A373" s="1">
+      <c r="A373">
         <v>2954771</v>
       </c>
       <c r="B373" t="s">
@@ -19109,7 +19083,7 @@
       </c>
     </row>
     <row r="374" spans="1:16">
-      <c r="A374" s="1">
+      <c r="A374">
         <v>2954772</v>
       </c>
       <c r="B374" t="s">
@@ -19159,7 +19133,7 @@
       </c>
     </row>
     <row r="375" spans="1:16">
-      <c r="A375" s="1">
+      <c r="A375">
         <v>2956048</v>
       </c>
       <c r="B375" t="s">
@@ -19209,7 +19183,7 @@
       </c>
     </row>
     <row r="376" spans="1:16">
-      <c r="A376" s="1">
+      <c r="A376">
         <v>2956049</v>
       </c>
       <c r="B376" t="s">
@@ -19259,7 +19233,7 @@
       </c>
     </row>
     <row r="377" spans="1:16">
-      <c r="A377" s="1">
+      <c r="A377">
         <v>2956050</v>
       </c>
       <c r="B377" t="s">
@@ -19309,7 +19283,7 @@
       </c>
     </row>
     <row r="378" spans="1:16">
-      <c r="A378" s="1">
+      <c r="A378">
         <v>2958920</v>
       </c>
       <c r="B378" t="s">
@@ -19356,7 +19330,7 @@
       </c>
     </row>
     <row r="379" spans="1:16">
-      <c r="A379" s="1">
+      <c r="A379">
         <v>2958921</v>
       </c>
       <c r="B379" t="s">
@@ -19403,7 +19377,7 @@
       </c>
     </row>
     <row r="380" spans="1:16">
-      <c r="A380" s="1">
+      <c r="A380">
         <v>2958922</v>
       </c>
       <c r="B380" t="s">
@@ -19450,7 +19424,7 @@
       </c>
     </row>
     <row r="381" spans="1:16">
-      <c r="A381" s="1">
+      <c r="A381">
         <v>2959561</v>
       </c>
       <c r="B381" t="s">
@@ -19500,7 +19474,7 @@
       </c>
     </row>
     <row r="382" spans="1:16">
-      <c r="A382" s="1">
+      <c r="A382">
         <v>2959562</v>
       </c>
       <c r="B382" t="s">
@@ -19550,7 +19524,7 @@
       </c>
     </row>
     <row r="383" spans="1:16">
-      <c r="A383" s="1">
+      <c r="A383">
         <v>2959563</v>
       </c>
       <c r="B383" t="s">
@@ -19600,7 +19574,7 @@
       </c>
     </row>
     <row r="384" spans="1:16">
-      <c r="A384" s="1">
+      <c r="A384">
         <v>2959710</v>
       </c>
       <c r="B384" t="s">
@@ -19650,7 +19624,7 @@
       </c>
     </row>
     <row r="385" spans="1:16">
-      <c r="A385" s="1">
+      <c r="A385">
         <v>2959711</v>
       </c>
       <c r="B385" t="s">
@@ -19700,7 +19674,7 @@
       </c>
     </row>
     <row r="386" spans="1:16">
-      <c r="A386" s="1">
+      <c r="A386">
         <v>2959768</v>
       </c>
       <c r="B386" t="s">
@@ -19750,7 +19724,7 @@
       </c>
     </row>
     <row r="387" spans="1:16">
-      <c r="A387" s="1">
+      <c r="A387">
         <v>2959769</v>
       </c>
       <c r="B387" t="s">
@@ -19800,7 +19774,7 @@
       </c>
     </row>
     <row r="388" spans="1:16">
-      <c r="A388" s="1">
+      <c r="A388">
         <v>2959770</v>
       </c>
       <c r="B388" t="s">
@@ -19850,7 +19824,7 @@
       </c>
     </row>
     <row r="389" spans="1:16">
-      <c r="A389" s="1">
+      <c r="A389">
         <v>2960215</v>
       </c>
       <c r="B389" t="s">
@@ -19900,7 +19874,7 @@
       </c>
     </row>
     <row r="390" spans="1:16">
-      <c r="A390" s="1">
+      <c r="A390">
         <v>2960216</v>
       </c>
       <c r="B390" t="s">
@@ -19950,7 +19924,7 @@
       </c>
     </row>
     <row r="391" spans="1:16">
-      <c r="A391" s="1">
+      <c r="A391">
         <v>2960217</v>
       </c>
       <c r="B391" t="s">
@@ -20000,7 +19974,7 @@
       </c>
     </row>
     <row r="392" spans="1:16">
-      <c r="A392" s="1">
+      <c r="A392">
         <v>2961700</v>
       </c>
       <c r="B392" t="s">
@@ -20050,7 +20024,7 @@
       </c>
     </row>
     <row r="393" spans="1:16">
-      <c r="A393" s="1">
+      <c r="A393">
         <v>2961701</v>
       </c>
       <c r="B393" t="s">
@@ -20100,7 +20074,7 @@
       </c>
     </row>
     <row r="394" spans="1:16">
-      <c r="A394" s="1">
+      <c r="A394">
         <v>2961702</v>
       </c>
       <c r="B394" t="s">
@@ -20150,7 +20124,7 @@
       </c>
     </row>
     <row r="395" spans="1:16">
-      <c r="A395" s="1">
+      <c r="A395">
         <v>2962636</v>
       </c>
       <c r="B395" t="s">
@@ -20200,7 +20174,7 @@
       </c>
     </row>
     <row r="396" spans="1:16">
-      <c r="A396" s="1">
+      <c r="A396">
         <v>2962787</v>
       </c>
       <c r="B396" t="s">
@@ -20250,7 +20224,7 @@
       </c>
     </row>
     <row r="397" spans="1:16">
-      <c r="A397" s="1">
+      <c r="A397">
         <v>2962788</v>
       </c>
       <c r="B397" t="s">
@@ -20297,7 +20271,7 @@
       </c>
     </row>
     <row r="398" spans="1:16">
-      <c r="A398" s="1">
+      <c r="A398">
         <v>2962789</v>
       </c>
       <c r="B398" t="s">
@@ -20344,7 +20318,7 @@
       </c>
     </row>
     <row r="399" spans="1:16">
-      <c r="A399" s="1">
+      <c r="A399">
         <v>2962955</v>
       </c>
       <c r="B399" t="s">
@@ -20391,7 +20365,7 @@
       </c>
     </row>
     <row r="400" spans="1:16">
-      <c r="A400" s="1">
+      <c r="A400">
         <v>2962956</v>
       </c>
       <c r="B400" t="s">
@@ -20438,7 +20412,7 @@
       </c>
     </row>
     <row r="401" spans="1:16">
-      <c r="A401" s="1">
+      <c r="A401">
         <v>2962957</v>
       </c>
       <c r="B401" t="s">
@@ -20485,7 +20459,7 @@
       </c>
     </row>
     <row r="402" spans="1:16">
-      <c r="A402" s="1">
+      <c r="A402">
         <v>2962985</v>
       </c>
       <c r="B402" t="s">
@@ -20535,7 +20509,7 @@
       </c>
     </row>
     <row r="403" spans="1:16">
-      <c r="A403" s="1">
+      <c r="A403">
         <v>2962986</v>
       </c>
       <c r="B403" t="s">
@@ -20585,7 +20559,7 @@
       </c>
     </row>
     <row r="404" spans="1:16">
-      <c r="A404" s="1">
+      <c r="A404">
         <v>2962987</v>
       </c>
       <c r="B404" t="s">
@@ -20635,7 +20609,7 @@
       </c>
     </row>
     <row r="405" spans="1:16">
-      <c r="A405" s="1">
+      <c r="A405">
         <v>2963086</v>
       </c>
       <c r="B405" t="s">
@@ -20685,7 +20659,7 @@
       </c>
     </row>
     <row r="406" spans="1:16">
-      <c r="A406" s="1">
+      <c r="A406">
         <v>2963087</v>
       </c>
       <c r="B406" t="s">
@@ -20732,7 +20706,7 @@
       </c>
     </row>
     <row r="407" spans="1:16">
-      <c r="A407" s="1">
+      <c r="A407">
         <v>2963088</v>
       </c>
       <c r="B407" t="s">
@@ -20782,7 +20756,7 @@
       </c>
     </row>
     <row r="408" spans="1:16">
-      <c r="A408" s="1">
+      <c r="A408">
         <v>2988112</v>
       </c>
       <c r="B408" t="s">
@@ -20832,7 +20806,7 @@
       </c>
     </row>
     <row r="409" spans="1:16">
-      <c r="A409" s="1">
+      <c r="A409">
         <v>2988113</v>
       </c>
       <c r="B409" t="s">
@@ -20882,7 +20856,7 @@
       </c>
     </row>
     <row r="410" spans="1:16">
-      <c r="A410" s="1">
+      <c r="A410">
         <v>2988114</v>
       </c>
       <c r="B410" t="s">
@@ -20932,7 +20906,7 @@
       </c>
     </row>
     <row r="411" spans="1:16">
-      <c r="A411" s="1">
+      <c r="A411">
         <v>2991815</v>
       </c>
       <c r="B411" t="s">
@@ -20982,7 +20956,7 @@
       </c>
     </row>
     <row r="412" spans="1:16">
-      <c r="A412" s="1">
+      <c r="A412">
         <v>2992648</v>
       </c>
       <c r="B412" t="s">
@@ -21032,7 +21006,7 @@
       </c>
     </row>
     <row r="413" spans="1:16">
-      <c r="A413" s="1">
+      <c r="A413">
         <v>2992649</v>
       </c>
       <c r="B413" t="s">
@@ -21082,7 +21056,7 @@
       </c>
     </row>
     <row r="414" spans="1:16">
-      <c r="A414" s="1">
+      <c r="A414">
         <v>2992650</v>
       </c>
       <c r="B414" t="s">
@@ -21132,7 +21106,7 @@
       </c>
     </row>
     <row r="415" spans="1:16">
-      <c r="A415" s="1">
+      <c r="A415">
         <v>2993577</v>
       </c>
       <c r="B415" t="s">
@@ -21182,7 +21156,7 @@
       </c>
     </row>
     <row r="416" spans="1:16">
-      <c r="A416" s="1">
+      <c r="A416">
         <v>2993578</v>
       </c>
       <c r="B416" t="s">
@@ -21232,7 +21206,7 @@
       </c>
     </row>
     <row r="417" spans="1:16">
-      <c r="A417" s="1">
+      <c r="A417">
         <v>2993996</v>
       </c>
       <c r="B417" t="s">
@@ -21282,7 +21256,7 @@
       </c>
     </row>
     <row r="418" spans="1:16">
-      <c r="A418" s="1">
+      <c r="A418">
         <v>2993997</v>
       </c>
       <c r="B418" t="s">
@@ -21332,7 +21306,7 @@
       </c>
     </row>
     <row r="419" spans="1:16">
-      <c r="A419" s="1">
+      <c r="A419">
         <v>2994725</v>
       </c>
       <c r="B419" t="s">
@@ -21382,7 +21356,7 @@
       </c>
     </row>
     <row r="420" spans="1:16">
-      <c r="A420" s="1">
+      <c r="A420">
         <v>2994726</v>
       </c>
       <c r="B420" t="s">
@@ -21432,7 +21406,7 @@
       </c>
     </row>
     <row r="421" spans="1:16">
-      <c r="A421" s="1">
+      <c r="A421">
         <v>2994727</v>
       </c>
       <c r="B421" t="s">
@@ -21482,7 +21456,7 @@
       </c>
     </row>
     <row r="422" spans="1:16">
-      <c r="A422" s="1">
+      <c r="A422">
         <v>2995783</v>
       </c>
       <c r="B422" t="s">
@@ -21532,7 +21506,7 @@
       </c>
     </row>
     <row r="423" spans="1:16">
-      <c r="A423" s="1">
+      <c r="A423">
         <v>2995784</v>
       </c>
       <c r="B423" t="s">
@@ -21582,7 +21556,7 @@
       </c>
     </row>
     <row r="424" spans="1:16">
-      <c r="A424" s="1">
+      <c r="A424">
         <v>2995785</v>
       </c>
       <c r="B424" t="s">
@@ -21632,7 +21606,7 @@
       </c>
     </row>
     <row r="425" spans="1:16">
-      <c r="A425" s="1">
+      <c r="A425">
         <v>2995816</v>
       </c>
       <c r="B425" t="s">
@@ -21682,7 +21656,7 @@
       </c>
     </row>
     <row r="426" spans="1:16">
-      <c r="A426" s="1">
+      <c r="A426">
         <v>2995817</v>
       </c>
       <c r="B426" t="s">
@@ -21732,7 +21706,7 @@
       </c>
     </row>
     <row r="427" spans="1:16">
-      <c r="A427" s="1">
+      <c r="A427">
         <v>2995818</v>
       </c>
       <c r="B427" t="s">
@@ -21782,7 +21756,7 @@
       </c>
     </row>
     <row r="428" spans="1:16">
-      <c r="A428" s="1">
+      <c r="A428">
         <v>2996150</v>
       </c>
       <c r="B428" t="s">
@@ -21832,7 +21806,7 @@
       </c>
     </row>
     <row r="429" spans="1:16">
-      <c r="A429" s="1">
+      <c r="A429">
         <v>2996164</v>
       </c>
       <c r="B429" t="s">
@@ -21882,7 +21856,7 @@
       </c>
     </row>
     <row r="430" spans="1:16">
-      <c r="A430" s="1">
+      <c r="A430">
         <v>2996295</v>
       </c>
       <c r="B430" t="s">
@@ -21932,7 +21906,7 @@
       </c>
     </row>
     <row r="431" spans="1:16">
-      <c r="A431" s="1">
+      <c r="A431">
         <v>2996296</v>
       </c>
       <c r="B431" t="s">
@@ -21982,7 +21956,7 @@
       </c>
     </row>
     <row r="432" spans="1:16">
-      <c r="A432" s="1">
+      <c r="A432">
         <v>2996298</v>
       </c>
       <c r="B432" t="s">
@@ -22032,7 +22006,7 @@
       </c>
     </row>
     <row r="433" spans="1:16">
-      <c r="A433" s="1">
+      <c r="A433">
         <v>2996299</v>
       </c>
       <c r="B433" t="s">
@@ -22082,7 +22056,7 @@
       </c>
     </row>
     <row r="434" spans="1:16">
-      <c r="A434" s="1">
+      <c r="A434">
         <v>2997955</v>
       </c>
       <c r="B434" t="s">
@@ -22132,7 +22106,7 @@
       </c>
     </row>
     <row r="435" spans="1:16">
-      <c r="A435" s="1">
+      <c r="A435">
         <v>2997956</v>
       </c>
       <c r="B435" t="s">
@@ -22182,7 +22156,7 @@
       </c>
     </row>
     <row r="436" spans="1:16">
-      <c r="A436" s="1">
+      <c r="A436">
         <v>2997957</v>
       </c>
       <c r="B436" t="s">
@@ -22232,7 +22206,7 @@
       </c>
     </row>
     <row r="437" spans="1:16">
-      <c r="A437" s="1">
+      <c r="A437">
         <v>3000269</v>
       </c>
       <c r="B437" t="s">
@@ -22282,7 +22256,7 @@
       </c>
     </row>
     <row r="438" spans="1:16">
-      <c r="A438" s="1">
+      <c r="A438">
         <v>3000270</v>
       </c>
       <c r="B438" t="s">
@@ -22332,7 +22306,7 @@
       </c>
     </row>
     <row r="439" spans="1:16">
-      <c r="A439" s="1">
+      <c r="A439">
         <v>3000287</v>
       </c>
       <c r="B439" t="s">
@@ -22382,7 +22356,7 @@
       </c>
     </row>
     <row r="440" spans="1:16">
-      <c r="A440" s="1">
+      <c r="A440">
         <v>3000288</v>
       </c>
       <c r="B440" t="s">
@@ -22432,7 +22406,7 @@
       </c>
     </row>
     <row r="441" spans="1:16">
-      <c r="A441" s="1">
+      <c r="A441">
         <v>3000289</v>
       </c>
       <c r="B441" t="s">
@@ -22482,7 +22456,7 @@
       </c>
     </row>
     <row r="442" spans="1:16">
-      <c r="A442" s="1">
+      <c r="A442">
         <v>3000290</v>
       </c>
       <c r="B442" t="s">
@@ -22532,7 +22506,7 @@
       </c>
     </row>
     <row r="443" spans="1:16">
-      <c r="A443" s="1">
+      <c r="A443">
         <v>3000614</v>
       </c>
       <c r="B443" t="s">
@@ -22582,7 +22556,7 @@
       </c>
     </row>
     <row r="444" spans="1:16">
-      <c r="A444" s="1">
+      <c r="A444">
         <v>3000615</v>
       </c>
       <c r="B444" t="s">
@@ -22632,7 +22606,7 @@
       </c>
     </row>
     <row r="445" spans="1:16">
-      <c r="A445" s="1">
+      <c r="A445">
         <v>3000616</v>
       </c>
       <c r="B445" t="s">
@@ -22679,7 +22653,7 @@
       </c>
     </row>
     <row r="446" spans="1:16">
-      <c r="A446" s="1">
+      <c r="A446">
         <v>3000617</v>
       </c>
       <c r="B446" t="s">
@@ -22729,7 +22703,7 @@
       </c>
     </row>
     <row r="447" spans="1:16">
-      <c r="A447" s="1">
+      <c r="A447">
         <v>3421228</v>
       </c>
       <c r="B447" t="s">
@@ -22779,7 +22753,7 @@
       </c>
     </row>
     <row r="448" spans="1:16">
-      <c r="A448" s="1">
+      <c r="A448">
         <v>3421229</v>
       </c>
       <c r="B448" t="s">
@@ -22829,7 +22803,7 @@
       </c>
     </row>
     <row r="449" spans="1:16">
-      <c r="A449" s="1">
+      <c r="A449">
         <v>3421230</v>
       </c>
       <c r="B449" t="s">
@@ -22876,7 +22850,7 @@
       </c>
     </row>
     <row r="450" spans="1:16">
-      <c r="A450" s="1">
+      <c r="A450">
         <v>3421231</v>
       </c>
       <c r="B450" t="s">
@@ -22926,7 +22900,7 @@
       </c>
     </row>
     <row r="451" spans="1:16">
-      <c r="A451" s="1">
+      <c r="A451">
         <v>3421986</v>
       </c>
       <c r="B451" t="s">
@@ -22976,7 +22950,7 @@
       </c>
     </row>
     <row r="452" spans="1:16">
-      <c r="A452" s="1">
+      <c r="A452">
         <v>3421987</v>
       </c>
       <c r="B452" t="s">
@@ -23026,7 +23000,7 @@
       </c>
     </row>
     <row r="453" spans="1:16">
-      <c r="A453" s="1">
+      <c r="A453">
         <v>3421988</v>
       </c>
       <c r="B453" t="s">
@@ -23073,7 +23047,7 @@
       </c>
     </row>
     <row r="454" spans="1:16">
-      <c r="A454" s="1">
+      <c r="A454">
         <v>3421989</v>
       </c>
       <c r="B454" t="s">
@@ -23120,7 +23094,7 @@
       </c>
     </row>
     <row r="455" spans="1:16">
-      <c r="A455" s="1">
+      <c r="A455">
         <v>3421990</v>
       </c>
       <c r="B455" t="s">
@@ -23170,7 +23144,7 @@
       </c>
     </row>
     <row r="456" spans="1:16">
-      <c r="A456" s="1">
+      <c r="A456">
         <v>3422397</v>
       </c>
       <c r="B456" t="s">
@@ -23220,7 +23194,7 @@
       </c>
     </row>
     <row r="457" spans="1:16">
-      <c r="A457" s="1">
+      <c r="A457">
         <v>3422398</v>
       </c>
       <c r="B457" t="s">
@@ -23270,7 +23244,7 @@
       </c>
     </row>
     <row r="458" spans="1:16">
-      <c r="A458" s="1">
+      <c r="A458">
         <v>3422399</v>
       </c>
       <c r="B458" t="s">
@@ -23317,7 +23291,7 @@
       </c>
     </row>
     <row r="459" spans="1:16">
-      <c r="A459" s="1">
+      <c r="A459">
         <v>3422400</v>
       </c>
       <c r="B459" t="s">
@@ -23367,7 +23341,7 @@
       </c>
     </row>
     <row r="460" spans="1:16">
-      <c r="A460" s="1">
+      <c r="A460">
         <v>3424469</v>
       </c>
       <c r="B460" t="s">
@@ -23417,7 +23391,7 @@
       </c>
     </row>
     <row r="461" spans="1:16">
-      <c r="A461" s="1">
+      <c r="A461">
         <v>3424470</v>
       </c>
       <c r="B461" t="s">
@@ -23467,7 +23441,7 @@
       </c>
     </row>
     <row r="462" spans="1:16">
-      <c r="A462" s="1">
+      <c r="A462">
         <v>3424471</v>
       </c>
       <c r="B462" t="s">
@@ -23514,7 +23488,7 @@
       </c>
     </row>
     <row r="463" spans="1:16">
-      <c r="A463" s="1">
+      <c r="A463">
         <v>3424472</v>
       </c>
       <c r="B463" t="s">
@@ -23561,7 +23535,7 @@
       </c>
     </row>
     <row r="464" spans="1:16">
-      <c r="A464" s="1">
+      <c r="A464">
         <v>3424473</v>
       </c>
       <c r="B464" t="s">
@@ -23611,7 +23585,7 @@
       </c>
     </row>
     <row r="465" spans="1:16">
-      <c r="A465" s="1">
+      <c r="A465">
         <v>3429471</v>
       </c>
       <c r="B465" t="s">
@@ -23661,7 +23635,7 @@
       </c>
     </row>
     <row r="466" spans="1:16">
-      <c r="A466" s="1">
+      <c r="A466">
         <v>3429472</v>
       </c>
       <c r="B466" t="s">
@@ -23711,7 +23685,7 @@
       </c>
     </row>
     <row r="467" spans="1:16">
-      <c r="A467" s="1">
+      <c r="A467">
         <v>3429473</v>
       </c>
       <c r="B467" t="s">
@@ -23758,7 +23732,7 @@
       </c>
     </row>
     <row r="468" spans="1:16">
-      <c r="A468" s="1">
+      <c r="A468">
         <v>3429474</v>
       </c>
       <c r="B468" t="s">
@@ -23805,7 +23779,7 @@
       </c>
     </row>
     <row r="469" spans="1:16">
-      <c r="A469" s="1">
+      <c r="A469">
         <v>3429475</v>
       </c>
       <c r="B469" t="s">
@@ -23855,7 +23829,7 @@
       </c>
     </row>
     <row r="470" spans="1:16">
-      <c r="A470" s="1">
+      <c r="A470">
         <v>3431095</v>
       </c>
       <c r="B470" t="s">
@@ -23905,7 +23879,7 @@
       </c>
     </row>
     <row r="471" spans="1:16">
-      <c r="A471" s="1">
+      <c r="A471">
         <v>3431096</v>
       </c>
       <c r="B471" t="s">
@@ -23955,7 +23929,7 @@
       </c>
     </row>
     <row r="472" spans="1:16">
-      <c r="A472" s="1">
+      <c r="A472">
         <v>3431097</v>
       </c>
       <c r="B472" t="s">
@@ -24002,7 +23976,7 @@
       </c>
     </row>
     <row r="473" spans="1:16">
-      <c r="A473" s="1">
+      <c r="A473">
         <v>3431098</v>
       </c>
       <c r="B473" t="s">
@@ -24052,7 +24026,7 @@
       </c>
     </row>
     <row r="474" spans="1:16">
-      <c r="A474" s="1">
+      <c r="A474">
         <v>3431575</v>
       </c>
       <c r="B474" t="s">
@@ -24102,7 +24076,7 @@
       </c>
     </row>
     <row r="475" spans="1:16">
-      <c r="A475" s="1">
+      <c r="A475">
         <v>3431576</v>
       </c>
       <c r="B475" t="s">
@@ -24152,7 +24126,7 @@
       </c>
     </row>
     <row r="476" spans="1:16">
-      <c r="A476" s="1">
+      <c r="A476">
         <v>3431577</v>
       </c>
       <c r="B476" t="s">
@@ -24199,7 +24173,7 @@
       </c>
     </row>
     <row r="477" spans="1:16">
-      <c r="A477" s="1">
+      <c r="A477">
         <v>3431578</v>
       </c>
       <c r="B477" t="s">
@@ -24246,7 +24220,7 @@
       </c>
     </row>
     <row r="478" spans="1:16">
-      <c r="A478" s="1">
+      <c r="A478">
         <v>3431579</v>
       </c>
       <c r="B478" t="s">
@@ -24296,7 +24270,7 @@
       </c>
     </row>
     <row r="479" spans="1:16">
-      <c r="A479" s="1">
+      <c r="A479">
         <v>3432022</v>
       </c>
       <c r="B479" t="s">
@@ -24346,7 +24320,7 @@
       </c>
     </row>
     <row r="480" spans="1:16">
-      <c r="A480" s="1">
+      <c r="A480">
         <v>3432023</v>
       </c>
       <c r="B480" t="s">
@@ -24396,7 +24370,7 @@
       </c>
     </row>
     <row r="481" spans="1:16">
-      <c r="A481" s="1">
+      <c r="A481">
         <v>3432024</v>
       </c>
       <c r="B481" t="s">
@@ -24443,7 +24417,7 @@
       </c>
     </row>
     <row r="482" spans="1:16">
-      <c r="A482" s="1">
+      <c r="A482">
         <v>3432025</v>
       </c>
       <c r="B482" t="s">
@@ -24493,7 +24467,7 @@
       </c>
     </row>
     <row r="483" spans="1:16">
-      <c r="A483" s="1">
+      <c r="A483">
         <v>3434055</v>
       </c>
       <c r="B483" t="s">
@@ -24543,7 +24517,7 @@
       </c>
     </row>
     <row r="484" spans="1:16">
-      <c r="A484" s="1">
+      <c r="A484">
         <v>3434056</v>
       </c>
       <c r="B484" t="s">
@@ -24593,7 +24567,7 @@
       </c>
     </row>
     <row r="485" spans="1:16">
-      <c r="A485" s="1">
+      <c r="A485">
         <v>3434057</v>
       </c>
       <c r="B485" t="s">
@@ -24640,7 +24614,7 @@
       </c>
     </row>
     <row r="486" spans="1:16">
-      <c r="A486" s="1">
+      <c r="A486">
         <v>3434058</v>
       </c>
       <c r="B486" t="s">
@@ -24690,7 +24664,7 @@
       </c>
     </row>
     <row r="487" spans="1:16">
-      <c r="A487" s="1">
+      <c r="A487">
         <v>3436346</v>
       </c>
       <c r="B487" t="s">
@@ -24740,7 +24714,7 @@
       </c>
     </row>
     <row r="488" spans="1:16">
-      <c r="A488" s="1">
+      <c r="A488">
         <v>3436347</v>
       </c>
       <c r="B488" t="s">
@@ -24790,7 +24764,7 @@
       </c>
     </row>
     <row r="489" spans="1:16">
-      <c r="A489" s="1">
+      <c r="A489">
         <v>3436348</v>
       </c>
       <c r="B489" t="s">
@@ -24837,7 +24811,7 @@
       </c>
     </row>
     <row r="490" spans="1:16">
-      <c r="A490" s="1">
+      <c r="A490">
         <v>3436349</v>
       </c>
       <c r="B490" t="s">
@@ -24884,7 +24858,7 @@
       </c>
     </row>
     <row r="491" spans="1:16">
-      <c r="A491" s="1">
+      <c r="A491">
         <v>3436350</v>
       </c>
       <c r="B491" t="s">
@@ -24934,7 +24908,7 @@
       </c>
     </row>
     <row r="492" spans="1:16">
-      <c r="A492" s="1">
+      <c r="A492">
         <v>3439144</v>
       </c>
       <c r="B492" t="s">
@@ -24984,7 +24958,7 @@
       </c>
     </row>
     <row r="493" spans="1:16">
-      <c r="A493" s="1">
+      <c r="A493">
         <v>3439145</v>
       </c>
       <c r="B493" t="s">
@@ -25034,7 +25008,7 @@
       </c>
     </row>
     <row r="494" spans="1:16">
-      <c r="A494" s="1">
+      <c r="A494">
         <v>3439146</v>
       </c>
       <c r="B494" t="s">
@@ -25081,7 +25055,7 @@
       </c>
     </row>
     <row r="495" spans="1:16">
-      <c r="A495" s="1">
+      <c r="A495">
         <v>3439147</v>
       </c>
       <c r="B495" t="s">
@@ -25128,7 +25102,7 @@
       </c>
     </row>
     <row r="496" spans="1:16">
-      <c r="A496" s="1">
+      <c r="A496">
         <v>3439148</v>
       </c>
       <c r="B496" t="s">
@@ -25178,7 +25152,7 @@
       </c>
     </row>
     <row r="497" spans="1:16">
-      <c r="A497" s="1">
+      <c r="A497">
         <v>3440421</v>
       </c>
       <c r="B497" t="s">
@@ -25228,7 +25202,7 @@
       </c>
     </row>
     <row r="498" spans="1:16">
-      <c r="A498" s="1">
+      <c r="A498">
         <v>3440422</v>
       </c>
       <c r="B498" t="s">
@@ -25278,7 +25252,7 @@
       </c>
     </row>
     <row r="499" spans="1:16">
-      <c r="A499" s="1">
+      <c r="A499">
         <v>3440423</v>
       </c>
       <c r="B499" t="s">
@@ -25325,7 +25299,7 @@
       </c>
     </row>
     <row r="500" spans="1:16">
-      <c r="A500" s="1">
+      <c r="A500">
         <v>3440424</v>
       </c>
       <c r="B500" t="s">
@@ -25375,7 +25349,7 @@
       </c>
     </row>
     <row r="501" spans="1:16">
-      <c r="A501" s="1">
+      <c r="A501">
         <v>4026801</v>
       </c>
       <c r="B501" t="s">
@@ -25425,7 +25399,7 @@
       </c>
     </row>
     <row r="502" spans="1:16">
-      <c r="A502" s="1">
+      <c r="A502">
         <v>4026802</v>
       </c>
       <c r="B502" t="s">
@@ -25475,7 +25449,7 @@
       </c>
     </row>
     <row r="503" spans="1:16">
-      <c r="A503" s="1">
+      <c r="A503">
         <v>4026803</v>
       </c>
       <c r="B503" t="s">
@@ -25525,7 +25499,7 @@
       </c>
     </row>
     <row r="504" spans="1:16">
-      <c r="A504" s="1">
+      <c r="A504">
         <v>4026804</v>
       </c>
       <c r="B504" t="s">
@@ -25575,7 +25549,7 @@
       </c>
     </row>
     <row r="505" spans="1:16">
-      <c r="A505" s="1">
+      <c r="A505">
         <v>4027258</v>
       </c>
       <c r="B505" t="s">
@@ -25625,7 +25599,7 @@
       </c>
     </row>
     <row r="506" spans="1:16">
-      <c r="A506" s="1">
+      <c r="A506">
         <v>4027259</v>
       </c>
       <c r="B506" t="s">
@@ -25675,7 +25649,7 @@
       </c>
     </row>
     <row r="507" spans="1:16">
-      <c r="A507" s="1">
+      <c r="A507">
         <v>4027260</v>
       </c>
       <c r="B507" t="s">
@@ -25725,7 +25699,7 @@
       </c>
     </row>
     <row r="508" spans="1:16">
-      <c r="A508" s="1">
+      <c r="A508">
         <v>4027261</v>
       </c>
       <c r="B508" t="s">
@@ -25775,7 +25749,7 @@
       </c>
     </row>
     <row r="509" spans="1:16">
-      <c r="A509" s="1">
+      <c r="A509">
         <v>4028082</v>
       </c>
       <c r="B509" t="s">
@@ -25825,7 +25799,7 @@
       </c>
     </row>
     <row r="510" spans="1:16">
-      <c r="A510" s="1">
+      <c r="A510">
         <v>4028083</v>
       </c>
       <c r="B510" t="s">
@@ -25875,7 +25849,7 @@
       </c>
     </row>
     <row r="511" spans="1:16">
-      <c r="A511" s="1">
+      <c r="A511">
         <v>4028084</v>
       </c>
       <c r="B511" t="s">
@@ -25925,7 +25899,7 @@
       </c>
     </row>
     <row r="512" spans="1:16">
-      <c r="A512" s="1">
+      <c r="A512">
         <v>4028085</v>
       </c>
       <c r="B512" t="s">
@@ -25975,7 +25949,7 @@
       </c>
     </row>
     <row r="513" spans="1:16">
-      <c r="A513" s="1">
+      <c r="A513">
         <v>4028086</v>
       </c>
       <c r="B513" t="s">
@@ -26025,7 +25999,7 @@
       </c>
     </row>
     <row r="514" spans="1:16">
-      <c r="A514" s="1">
+      <c r="A514">
         <v>4029706</v>
       </c>
       <c r="B514" t="s">
@@ -26075,7 +26049,7 @@
       </c>
     </row>
     <row r="515" spans="1:16">
-      <c r="A515" s="1">
+      <c r="A515">
         <v>4029707</v>
       </c>
       <c r="B515" t="s">
@@ -26122,7 +26096,7 @@
       </c>
     </row>
     <row r="516" spans="1:16">
-      <c r="A516" s="1">
+      <c r="A516">
         <v>4029708</v>
       </c>
       <c r="B516" t="s">
@@ -26169,7 +26143,7 @@
       </c>
     </row>
     <row r="517" spans="1:16">
-      <c r="A517" s="1">
+      <c r="A517">
         <v>4029709</v>
       </c>
       <c r="B517" t="s">
@@ -26219,7 +26193,7 @@
       </c>
     </row>
     <row r="518" spans="1:16">
-      <c r="A518" s="1">
+      <c r="A518">
         <v>4029838</v>
       </c>
       <c r="B518" t="s">
@@ -26269,7 +26243,7 @@
       </c>
     </row>
     <row r="519" spans="1:16">
-      <c r="A519" s="1">
+      <c r="A519">
         <v>4029839</v>
       </c>
       <c r="B519" t="s">
@@ -26319,7 +26293,7 @@
       </c>
     </row>
     <row r="520" spans="1:16">
-      <c r="A520" s="1">
+      <c r="A520">
         <v>4029840</v>
       </c>
       <c r="B520" t="s">
@@ -26369,7 +26343,7 @@
       </c>
     </row>
     <row r="521" spans="1:16">
-      <c r="A521" s="1">
+      <c r="A521">
         <v>4029841</v>
       </c>
       <c r="B521" t="s">
@@ -26419,7 +26393,7 @@
       </c>
     </row>
     <row r="522" spans="1:16">
-      <c r="A522" s="1">
+      <c r="A522">
         <v>4030187</v>
       </c>
       <c r="B522" t="s">
@@ -26469,7 +26443,7 @@
       </c>
     </row>
     <row r="523" spans="1:16">
-      <c r="A523" s="1">
+      <c r="A523">
         <v>4030188</v>
       </c>
       <c r="B523" t="s">
@@ -26519,7 +26493,7 @@
       </c>
     </row>
     <row r="524" spans="1:16">
-      <c r="A524" s="1">
+      <c r="A524">
         <v>4030189</v>
       </c>
       <c r="B524" t="s">
@@ -26569,7 +26543,7 @@
       </c>
     </row>
     <row r="525" spans="1:16">
-      <c r="A525" s="1">
+      <c r="A525">
         <v>4030358</v>
       </c>
       <c r="B525" t="s">
@@ -26619,7 +26593,7 @@
       </c>
     </row>
     <row r="526" spans="1:16">
-      <c r="A526" s="1">
+      <c r="A526">
         <v>4030359</v>
       </c>
       <c r="B526" t="s">
@@ -26669,7 +26643,7 @@
       </c>
     </row>
     <row r="527" spans="1:16">
-      <c r="A527" s="1">
+      <c r="A527">
         <v>4030360</v>
       </c>
       <c r="B527" t="s">
@@ -26719,7 +26693,7 @@
       </c>
     </row>
     <row r="528" spans="1:16">
-      <c r="A528" s="1">
+      <c r="A528">
         <v>4030361</v>
       </c>
       <c r="B528" t="s">
@@ -26769,7 +26743,7 @@
       </c>
     </row>
     <row r="529" spans="1:16">
-      <c r="A529" s="1">
+      <c r="A529">
         <v>4030849</v>
       </c>
       <c r="B529" t="s">
@@ -26819,7 +26793,7 @@
       </c>
     </row>
     <row r="530" spans="1:16">
-      <c r="A530" s="1">
+      <c r="A530">
         <v>4030850</v>
       </c>
       <c r="B530" t="s">
@@ -26866,7 +26840,7 @@
       </c>
     </row>
     <row r="531" spans="1:16">
-      <c r="A531" s="1">
+      <c r="A531">
         <v>4030851</v>
       </c>
       <c r="B531" t="s">
@@ -26913,7 +26887,7 @@
       </c>
     </row>
     <row r="532" spans="1:16">
-      <c r="A532" s="1">
+      <c r="A532">
         <v>4030852</v>
       </c>
       <c r="B532" t="s">
@@ -26963,7 +26937,7 @@
       </c>
     </row>
     <row r="533" spans="1:16">
-      <c r="A533" s="1">
+      <c r="A533">
         <v>4032277</v>
       </c>
       <c r="B533" t="s">
@@ -27013,7 +26987,7 @@
       </c>
     </row>
     <row r="534" spans="1:16">
-      <c r="A534" s="1">
+      <c r="A534">
         <v>4032469</v>
       </c>
       <c r="B534" t="s">
@@ -27063,7 +27037,7 @@
       </c>
     </row>
     <row r="535" spans="1:16">
-      <c r="A535" s="1">
+      <c r="A535">
         <v>4032470</v>
       </c>
       <c r="B535" t="s">
@@ -27113,7 +27087,7 @@
       </c>
     </row>
     <row r="536" spans="1:16">
-      <c r="A536" s="1">
+      <c r="A536">
         <v>4033449</v>
       </c>
       <c r="B536" t="s">
@@ -27163,7 +27137,7 @@
       </c>
     </row>
     <row r="537" spans="1:16">
-      <c r="A537" s="1">
+      <c r="A537">
         <v>4033450</v>
       </c>
       <c r="B537" t="s">
@@ -27210,7 +27184,7 @@
       </c>
     </row>
     <row r="538" spans="1:16">
-      <c r="A538" s="1">
+      <c r="A538">
         <v>4033451</v>
       </c>
       <c r="B538" t="s">
@@ -27260,7 +27234,7 @@
       </c>
     </row>
     <row r="539" spans="1:16">
-      <c r="A539" s="1">
+      <c r="A539">
         <v>4033910</v>
       </c>
       <c r="B539" t="s">
@@ -27310,7 +27284,7 @@
       </c>
     </row>
     <row r="540" spans="1:16">
-      <c r="A540" s="1">
+      <c r="A540">
         <v>4033911</v>
       </c>
       <c r="B540" t="s">
@@ -27357,7 +27331,7 @@
       </c>
     </row>
     <row r="541" spans="1:16">
-      <c r="A541" s="1">
+      <c r="A541">
         <v>4033912</v>
       </c>
       <c r="B541" t="s">
@@ -27404,7 +27378,7 @@
       </c>
     </row>
     <row r="542" spans="1:16">
-      <c r="A542" s="1">
+      <c r="A542">
         <v>4033913</v>
       </c>
       <c r="B542" t="s">
@@ -27454,7 +27428,7 @@
       </c>
     </row>
     <row r="543" spans="1:16">
-      <c r="A543" s="1">
+      <c r="A543">
         <v>4034281</v>
       </c>
       <c r="B543" t="s">
@@ -27504,7 +27478,7 @@
       </c>
     </row>
     <row r="544" spans="1:16">
-      <c r="A544" s="1">
+      <c r="A544">
         <v>4034282</v>
       </c>
       <c r="B544" t="s">
@@ -27554,7 +27528,7 @@
       </c>
     </row>
     <row r="545" spans="1:16">
-      <c r="A545" s="1">
+      <c r="A545">
         <v>4034283</v>
       </c>
       <c r="B545" t="s">
@@ -27604,7 +27578,7 @@
       </c>
     </row>
     <row r="546" spans="1:16">
-      <c r="A546" s="1">
+      <c r="A546">
         <v>4034284</v>
       </c>
       <c r="B546" t="s">
@@ -27654,7 +27628,7 @@
       </c>
     </row>
     <row r="547" spans="1:16">
-      <c r="A547" s="1">
+      <c r="A547">
         <v>4034285</v>
       </c>
       <c r="B547" t="s">
@@ -27704,7 +27678,7 @@
       </c>
     </row>
     <row r="548" spans="1:16">
-      <c r="A548" s="1">
+      <c r="A548">
         <v>4034360</v>
       </c>
       <c r="B548" t="s">
@@ -27754,7 +27728,7 @@
       </c>
     </row>
     <row r="549" spans="1:16">
-      <c r="A549" s="1">
+      <c r="A549">
         <v>4106768</v>
       </c>
       <c r="B549" t="s">
@@ -27804,7 +27778,7 @@
       </c>
     </row>
     <row r="550" spans="1:16">
-      <c r="A550" s="1">
+      <c r="A550">
         <v>4106769</v>
       </c>
       <c r="B550" t="s">
@@ -27851,7 +27825,7 @@
       </c>
     </row>
     <row r="551" spans="1:16">
-      <c r="A551" s="1">
+      <c r="A551">
         <v>4106770</v>
       </c>
       <c r="B551" t="s">
@@ -27898,7 +27872,7 @@
       </c>
     </row>
     <row r="552" spans="1:16">
-      <c r="A552" s="1">
+      <c r="A552">
         <v>4106771</v>
       </c>
       <c r="B552" t="s">
@@ -27948,7 +27922,7 @@
       </c>
     </row>
     <row r="553" spans="1:16">
-      <c r="A553" s="1">
+      <c r="A553">
         <v>4107742</v>
       </c>
       <c r="B553" t="s">
@@ -27998,7 +27972,7 @@
       </c>
     </row>
     <row r="554" spans="1:16">
-      <c r="A554" s="1">
+      <c r="A554">
         <v>4107743</v>
       </c>
       <c r="B554" t="s">
@@ -28045,7 +28019,7 @@
       </c>
     </row>
     <row r="555" spans="1:16">
-      <c r="A555" s="1">
+      <c r="A555">
         <v>4107744</v>
       </c>
       <c r="B555" t="s">
@@ -28095,7 +28069,7 @@
       </c>
     </row>
     <row r="556" spans="1:16">
-      <c r="A556" s="1">
+      <c r="A556">
         <v>4107745</v>
       </c>
       <c r="B556" t="s">
@@ -28145,7 +28119,7 @@
       </c>
     </row>
     <row r="557" spans="1:16">
-      <c r="A557" s="1">
+      <c r="A557">
         <v>4109671</v>
       </c>
       <c r="B557" t="s">
@@ -28195,7 +28169,7 @@
       </c>
     </row>
     <row r="558" spans="1:16">
-      <c r="A558" s="1">
+      <c r="A558">
         <v>4109672</v>
       </c>
       <c r="B558" t="s">
@@ -28245,7 +28219,7 @@
       </c>
     </row>
     <row r="559" spans="1:16">
-      <c r="A559" s="1">
+      <c r="A559">
         <v>4110300</v>
       </c>
       <c r="B559" t="s">
@@ -28295,7 +28269,7 @@
       </c>
     </row>
     <row r="560" spans="1:16">
-      <c r="A560" s="1">
+      <c r="A560">
         <v>4110301</v>
       </c>
       <c r="B560" t="s">
@@ -28345,7 +28319,7 @@
       </c>
     </row>
     <row r="561" spans="1:16">
-      <c r="A561" s="1">
+      <c r="A561">
         <v>4110302</v>
       </c>
       <c r="B561" t="s">
@@ -28395,7 +28369,7 @@
       </c>
     </row>
     <row r="562" spans="1:16">
-      <c r="A562" s="1">
+      <c r="A562">
         <v>4110734</v>
       </c>
       <c r="B562" t="s">
@@ -28445,7 +28419,7 @@
       </c>
     </row>
     <row r="563" spans="1:16">
-      <c r="A563" s="1">
+      <c r="A563">
         <v>4110735</v>
       </c>
       <c r="B563" t="s">
@@ -28495,7 +28469,7 @@
       </c>
     </row>
     <row r="564" spans="1:16">
-      <c r="A564" s="1">
+      <c r="A564">
         <v>4112329</v>
       </c>
       <c r="B564" t="s">
@@ -28545,7 +28519,7 @@
       </c>
     </row>
     <row r="565" spans="1:16">
-      <c r="A565" s="1">
+      <c r="A565">
         <v>4112330</v>
       </c>
       <c r="B565" t="s">
@@ -28592,7 +28566,7 @@
       </c>
     </row>
     <row r="566" spans="1:16">
-      <c r="A566" s="1">
+      <c r="A566">
         <v>4112331</v>
       </c>
       <c r="B566" t="s">
@@ -28642,7 +28616,7 @@
       </c>
     </row>
     <row r="567" spans="1:16">
-      <c r="A567" s="1">
+      <c r="A567">
         <v>4116179</v>
       </c>
       <c r="B567" t="s">
@@ -28692,7 +28666,7 @@
       </c>
     </row>
     <row r="568" spans="1:16">
-      <c r="A568" s="1">
+      <c r="A568">
         <v>4116180</v>
       </c>
       <c r="B568" t="s">
@@ -28739,7 +28713,7 @@
       </c>
     </row>
     <row r="569" spans="1:16">
-      <c r="A569" s="1">
+      <c r="A569">
         <v>4116181</v>
       </c>
       <c r="B569" t="s">
@@ -28789,7 +28763,7 @@
       </c>
     </row>
     <row r="570" spans="1:16">
-      <c r="A570" s="1">
+      <c r="A570">
         <v>4116182</v>
       </c>
       <c r="B570" t="s">
@@ -28839,7 +28813,7 @@
       </c>
     </row>
     <row r="571" spans="1:16">
-      <c r="A571" s="1">
+      <c r="A571">
         <v>4117953</v>
       </c>
       <c r="B571" t="s">
@@ -28889,7 +28863,7 @@
       </c>
     </row>
     <row r="572" spans="1:16">
-      <c r="A572" s="1">
+      <c r="A572">
         <v>4117954</v>
       </c>
       <c r="B572" t="s">
@@ -28936,7 +28910,7 @@
       </c>
     </row>
     <row r="573" spans="1:16">
-      <c r="A573" s="1">
+      <c r="A573">
         <v>4117955</v>
       </c>
       <c r="B573" t="s">
@@ -28983,7 +28957,7 @@
       </c>
     </row>
     <row r="574" spans="1:16">
-      <c r="A574" s="1">
+      <c r="A574">
         <v>4117956</v>
       </c>
       <c r="B574" t="s">
@@ -29033,7 +29007,7 @@
       </c>
     </row>
     <row r="575" spans="1:16">
-      <c r="A575" s="1">
+      <c r="A575">
         <v>4119102</v>
       </c>
       <c r="B575" t="s">
@@ -29083,7 +29057,7 @@
       </c>
     </row>
     <row r="576" spans="1:16">
-      <c r="A576" s="1">
+      <c r="A576">
         <v>4119103</v>
       </c>
       <c r="B576" t="s">
@@ -29130,7 +29104,7 @@
       </c>
     </row>
     <row r="577" spans="1:16">
-      <c r="A577" s="1">
+      <c r="A577">
         <v>4119104</v>
       </c>
       <c r="B577" t="s">
@@ -29177,7 +29151,7 @@
       </c>
     </row>
     <row r="578" spans="1:16">
-      <c r="A578" s="1">
+      <c r="A578">
         <v>4119105</v>
       </c>
       <c r="B578" t="s">
@@ -29224,7 +29198,7 @@
       </c>
     </row>
     <row r="579" spans="1:16">
-      <c r="A579" s="1">
+      <c r="A579">
         <v>4119106</v>
       </c>
       <c r="B579" t="s">
@@ -29274,7 +29248,7 @@
       </c>
     </row>
     <row r="580" spans="1:16">
-      <c r="A580" s="1">
+      <c r="A580">
         <v>4121886</v>
       </c>
       <c r="B580" t="s">
@@ -29324,7 +29298,7 @@
       </c>
     </row>
     <row r="581" spans="1:16">
-      <c r="A581" s="1">
+      <c r="A581">
         <v>4121887</v>
       </c>
       <c r="B581" t="s">
@@ -29371,7 +29345,7 @@
       </c>
     </row>
     <row r="582" spans="1:16">
-      <c r="A582" s="1">
+      <c r="A582">
         <v>4121888</v>
       </c>
       <c r="B582" t="s">
@@ -29421,7 +29395,7 @@
       </c>
     </row>
     <row r="583" spans="1:16">
-      <c r="A583" s="1">
+      <c r="A583">
         <v>4125047</v>
       </c>
       <c r="B583" t="s">
@@ -29471,7 +29445,7 @@
       </c>
     </row>
     <row r="584" spans="1:16">
-      <c r="A584" s="1">
+      <c r="A584">
         <v>4125048</v>
       </c>
       <c r="B584" t="s">
@@ -29518,7 +29492,7 @@
       </c>
     </row>
     <row r="585" spans="1:16">
-      <c r="A585" s="1">
+      <c r="A585">
         <v>4125049</v>
       </c>
       <c r="B585" t="s">
@@ -29565,7 +29539,7 @@
       </c>
     </row>
     <row r="586" spans="1:16">
-      <c r="A586" s="1">
+      <c r="A586">
         <v>4125050</v>
       </c>
       <c r="B586" t="s">
@@ -29615,7 +29589,7 @@
       </c>
     </row>
     <row r="587" spans="1:16">
-      <c r="A587" s="1">
+      <c r="A587">
         <v>4125509</v>
       </c>
       <c r="B587" t="s">
@@ -29665,7 +29639,7 @@
       </c>
     </row>
     <row r="588" spans="1:16">
-      <c r="A588" s="1">
+      <c r="A588">
         <v>4125510</v>
       </c>
       <c r="B588" t="s">
@@ -29712,7 +29686,7 @@
       </c>
     </row>
     <row r="589" spans="1:16">
-      <c r="A589" s="1">
+      <c r="A589">
         <v>4125511</v>
       </c>
       <c r="B589" t="s">
@@ -29762,7 +29736,7 @@
       </c>
     </row>
     <row r="590" spans="1:16">
-      <c r="A590" s="1">
+      <c r="A590">
         <v>4126327</v>
       </c>
       <c r="B590" t="s">
@@ -29812,7 +29786,7 @@
       </c>
     </row>
     <row r="591" spans="1:16">
-      <c r="A591" s="1">
+      <c r="A591">
         <v>4126328</v>
       </c>
       <c r="B591" t="s">
@@ -29859,7 +29833,7 @@
       </c>
     </row>
     <row r="592" spans="1:16">
-      <c r="A592" s="1">
+      <c r="A592">
         <v>4126329</v>
       </c>
       <c r="B592" t="s">
@@ -29909,7 +29883,7 @@
       </c>
     </row>
     <row r="593" spans="1:16">
-      <c r="A593" s="1">
+      <c r="A593">
         <v>5243863</v>
       </c>
       <c r="B593" t="s">
@@ -29959,7 +29933,7 @@
       </c>
     </row>
     <row r="594" spans="1:16">
-      <c r="A594" s="1">
+      <c r="A594">
         <v>5243864</v>
       </c>
       <c r="B594" t="s">
@@ -30009,7 +29983,7 @@
       </c>
     </row>
     <row r="595" spans="1:16">
-      <c r="A595" s="1">
+      <c r="A595">
         <v>5243865</v>
       </c>
       <c r="B595" t="s">
@@ -30059,7 +30033,7 @@
       </c>
     </row>
     <row r="596" spans="1:16">
-      <c r="A596" s="1">
+      <c r="A596">
         <v>5244838</v>
       </c>
       <c r="B596" t="s">
@@ -30109,7 +30083,7 @@
       </c>
     </row>
     <row r="597" spans="1:16">
-      <c r="A597" s="1">
+      <c r="A597">
         <v>5244839</v>
       </c>
       <c r="B597" t="s">
@@ -30159,7 +30133,7 @@
       </c>
     </row>
     <row r="598" spans="1:16">
-      <c r="A598" s="1">
+      <c r="A598">
         <v>5244840</v>
       </c>
       <c r="B598" t="s">
@@ -30209,7 +30183,7 @@
       </c>
     </row>
     <row r="599" spans="1:16">
-      <c r="A599" s="1">
+      <c r="A599">
         <v>5245459</v>
       </c>
       <c r="B599" t="s">
@@ -30259,7 +30233,7 @@
       </c>
     </row>
     <row r="600" spans="1:16">
-      <c r="A600" s="1">
+      <c r="A600">
         <v>5245478</v>
       </c>
       <c r="B600" t="s">
@@ -30309,7 +30283,7 @@
       </c>
     </row>
     <row r="601" spans="1:16">
-      <c r="A601" s="1">
+      <c r="A601">
         <v>5245479</v>
       </c>
       <c r="B601" t="s">
@@ -30359,7 +30333,7 @@
       </c>
     </row>
     <row r="602" spans="1:16">
-      <c r="A602" s="1">
+      <c r="A602">
         <v>5245480</v>
       </c>
       <c r="B602" t="s">
@@ -30409,7 +30383,7 @@
       </c>
     </row>
     <row r="603" spans="1:16">
-      <c r="A603" s="1">
+      <c r="A603">
         <v>5245481</v>
       </c>
       <c r="B603" t="s">
@@ -30459,7 +30433,7 @@
       </c>
     </row>
     <row r="604" spans="1:16">
-      <c r="A604" s="1">
+      <c r="A604">
         <v>5245497</v>
       </c>
       <c r="B604" t="s">
@@ -30509,7 +30483,7 @@
       </c>
     </row>
     <row r="605" spans="1:16">
-      <c r="A605" s="1">
+      <c r="A605">
         <v>5245498</v>
       </c>
       <c r="B605" t="s">
@@ -30559,7 +30533,7 @@
       </c>
     </row>
     <row r="606" spans="1:16">
-      <c r="A606" s="1">
+      <c r="A606">
         <v>5245695</v>
       </c>
       <c r="B606" t="s">
@@ -30609,7 +30583,7 @@
       </c>
     </row>
     <row r="607" spans="1:16">
-      <c r="A607" s="1">
+      <c r="A607">
         <v>5245696</v>
       </c>
       <c r="B607" t="s">
@@ -30659,7 +30633,7 @@
       </c>
     </row>
     <row r="608" spans="1:16">
-      <c r="A608" s="1">
+      <c r="A608">
         <v>5245697</v>
       </c>
       <c r="B608" t="s">
@@ -30709,7 +30683,7 @@
       </c>
     </row>
     <row r="609" spans="1:16">
-      <c r="A609" s="1">
+      <c r="A609">
         <v>5247112</v>
       </c>
       <c r="B609" t="s">
@@ -30759,7 +30733,7 @@
       </c>
     </row>
     <row r="610" spans="1:16">
-      <c r="A610" s="1">
+      <c r="A610">
         <v>5247113</v>
       </c>
       <c r="B610" t="s">
@@ -30809,7 +30783,7 @@
       </c>
     </row>
     <row r="611" spans="1:16">
-      <c r="A611" s="1">
+      <c r="A611">
         <v>5247114</v>
       </c>
       <c r="B611" t="s">
@@ -30859,7 +30833,7 @@
       </c>
     </row>
     <row r="612" spans="1:16">
-      <c r="A612" s="1">
+      <c r="A612">
         <v>5247490</v>
       </c>
       <c r="B612" t="s">
@@ -30906,7 +30880,7 @@
       </c>
     </row>
     <row r="613" spans="1:16">
-      <c r="A613" s="1">
+      <c r="A613">
         <v>5247491</v>
       </c>
       <c r="B613" t="s">
@@ -30953,7 +30927,7 @@
       </c>
     </row>
     <row r="614" spans="1:16">
-      <c r="A614" s="1">
+      <c r="A614">
         <v>5247492</v>
       </c>
       <c r="B614" t="s">
@@ -31000,7 +30974,7 @@
       </c>
     </row>
     <row r="615" spans="1:16">
-      <c r="A615" s="1">
+      <c r="A615">
         <v>5247525</v>
       </c>
       <c r="B615" t="s">
@@ -31050,7 +31024,7 @@
       </c>
     </row>
     <row r="616" spans="1:16">
-      <c r="A616" s="1">
+      <c r="A616">
         <v>5247526</v>
       </c>
       <c r="B616" t="s">
@@ -31100,7 +31074,7 @@
       </c>
     </row>
     <row r="617" spans="1:16">
-      <c r="A617" s="1">
+      <c r="A617">
         <v>5247527</v>
       </c>
       <c r="B617" t="s">
@@ -31147,7 +31121,7 @@
       </c>
     </row>
     <row r="618" spans="1:16">
-      <c r="A618" s="1">
+      <c r="A618">
         <v>5247528</v>
       </c>
       <c r="B618" t="s">
@@ -31197,7 +31171,7 @@
       </c>
     </row>
     <row r="619" spans="1:16">
-      <c r="A619" s="1">
+      <c r="A619">
         <v>5247994</v>
       </c>
       <c r="B619" t="s">
@@ -31247,7 +31221,7 @@
       </c>
     </row>
     <row r="620" spans="1:16">
-      <c r="A620" s="1">
+      <c r="A620">
         <v>5247995</v>
       </c>
       <c r="B620" t="s">
@@ -31297,7 +31271,7 @@
       </c>
     </row>
     <row r="621" spans="1:16">
-      <c r="A621" s="1">
+      <c r="A621">
         <v>5247996</v>
       </c>
       <c r="B621" t="s">
@@ -31347,7 +31321,7 @@
       </c>
     </row>
     <row r="622" spans="1:16">
-      <c r="A622" s="1">
+      <c r="A622">
         <v>5250682</v>
       </c>
       <c r="B622" t="s">
@@ -31397,7 +31371,7 @@
       </c>
     </row>
     <row r="623" spans="1:16">
-      <c r="A623" s="1">
+      <c r="A623">
         <v>5250683</v>
       </c>
       <c r="B623" t="s">
@@ -31447,7 +31421,7 @@
       </c>
     </row>
     <row r="624" spans="1:16">
-      <c r="A624" s="1">
+      <c r="A624">
         <v>5250684</v>
       </c>
       <c r="B624" t="s">
@@ -31497,7 +31471,7 @@
       </c>
     </row>
     <row r="625" spans="1:16">
-      <c r="A625" s="1">
+      <c r="A625">
         <v>5251562</v>
       </c>
       <c r="B625" t="s">
@@ -31547,7 +31521,7 @@
       </c>
     </row>
     <row r="626" spans="1:16">
-      <c r="A626" s="1">
+      <c r="A626">
         <v>5251563</v>
       </c>
       <c r="B626" t="s">
@@ -31594,7 +31568,7 @@
       </c>
     </row>
     <row r="627" spans="1:16">
-      <c r="A627" s="1">
+      <c r="A627">
         <v>5251564</v>
       </c>
       <c r="B627" t="s">
@@ -31641,7 +31615,7 @@
       </c>
     </row>
     <row r="628" spans="1:16">
-      <c r="A628" s="1">
+      <c r="A628">
         <v>5251565</v>
       </c>
       <c r="B628" t="s">
@@ -31691,7 +31665,7 @@
       </c>
     </row>
     <row r="629" spans="1:16">
-      <c r="A629" s="1">
+      <c r="A629">
         <v>5253195</v>
       </c>
       <c r="B629" t="s">
@@ -31741,7 +31715,7 @@
       </c>
     </row>
     <row r="630" spans="1:16">
-      <c r="A630" s="1">
+      <c r="A630">
         <v>5253196</v>
       </c>
       <c r="B630" t="s">
@@ -31791,7 +31765,7 @@
       </c>
     </row>
     <row r="631" spans="1:16">
-      <c r="A631" s="1">
+      <c r="A631">
         <v>5253197</v>
       </c>
       <c r="B631" t="s">
@@ -31841,7 +31815,7 @@
       </c>
     </row>
     <row r="632" spans="1:16">
-      <c r="A632" s="1">
+      <c r="A632">
         <v>5375064</v>
       </c>
       <c r="B632" t="s">
@@ -31891,7 +31865,7 @@
       </c>
     </row>
     <row r="633" spans="1:16">
-      <c r="A633" s="1">
+      <c r="A633">
         <v>5375065</v>
       </c>
       <c r="B633" t="s">
@@ -31941,7 +31915,7 @@
       </c>
     </row>
     <row r="634" spans="1:16">
-      <c r="A634" s="1">
+      <c r="A634">
         <v>5375066</v>
       </c>
       <c r="B634" t="s">
@@ -31991,7 +31965,7 @@
       </c>
     </row>
     <row r="635" spans="1:16">
-      <c r="A635" s="1">
+      <c r="A635">
         <v>5377563</v>
       </c>
       <c r="B635" t="s">
@@ -32041,7 +32015,7 @@
       </c>
     </row>
     <row r="636" spans="1:16">
-      <c r="A636" s="1">
+      <c r="A636">
         <v>5377564</v>
       </c>
       <c r="B636" t="s">
@@ -32091,7 +32065,7 @@
       </c>
     </row>
     <row r="637" spans="1:16">
-      <c r="A637" s="1">
+      <c r="A637">
         <v>5377565</v>
       </c>
       <c r="B637" t="s">
@@ -32141,7 +32115,7 @@
       </c>
     </row>
     <row r="638" spans="1:16">
-      <c r="A638" s="1">
+      <c r="A638">
         <v>5380573</v>
       </c>
       <c r="B638" t="s">
@@ -32191,7 +32165,7 @@
       </c>
     </row>
     <row r="639" spans="1:16">
-      <c r="A639" s="1">
+      <c r="A639">
         <v>5380574</v>
       </c>
       <c r="B639" t="s">
@@ -32241,7 +32215,7 @@
       </c>
     </row>
     <row r="640" spans="1:16">
-      <c r="A640" s="1">
+      <c r="A640">
         <v>5380575</v>
       </c>
       <c r="B640" t="s">
@@ -32291,7 +32265,7 @@
       </c>
     </row>
     <row r="641" spans="1:16">
-      <c r="A641" s="1">
+      <c r="A641">
         <v>5380887</v>
       </c>
       <c r="B641" t="s">
@@ -32341,7 +32315,7 @@
       </c>
     </row>
     <row r="642" spans="1:16">
-      <c r="A642" s="1">
+      <c r="A642">
         <v>5380888</v>
       </c>
       <c r="B642" t="s">
@@ -32391,7 +32365,7 @@
       </c>
     </row>
     <row r="643" spans="1:16">
-      <c r="A643" s="1">
+      <c r="A643">
         <v>5380889</v>
       </c>
       <c r="B643" t="s">
@@ -32441,7 +32415,7 @@
       </c>
     </row>
     <row r="644" spans="1:16">
-      <c r="A644" s="1">
+      <c r="A644">
         <v>5381593</v>
       </c>
       <c r="B644" t="s">
@@ -32491,7 +32465,7 @@
       </c>
     </row>
     <row r="645" spans="1:16">
-      <c r="A645" s="1">
+      <c r="A645">
         <v>5381594</v>
       </c>
       <c r="B645" t="s">
@@ -32541,7 +32515,7 @@
       </c>
     </row>
     <row r="646" spans="1:16">
-      <c r="A646" s="1">
+      <c r="A646">
         <v>5381595</v>
       </c>
       <c r="B646" t="s">
@@ -32591,7 +32565,7 @@
       </c>
     </row>
     <row r="647" spans="1:16">
-      <c r="A647" s="1">
+      <c r="A647">
         <v>5382337</v>
       </c>
       <c r="B647" t="s">
@@ -32641,7 +32615,7 @@
       </c>
     </row>
     <row r="648" spans="1:16">
-      <c r="A648" s="1">
+      <c r="A648">
         <v>5382338</v>
       </c>
       <c r="B648" t="s">
@@ -32691,7 +32665,7 @@
       </c>
     </row>
     <row r="649" spans="1:16">
-      <c r="A649" s="1">
+      <c r="A649">
         <v>5382339</v>
       </c>
       <c r="B649" t="s">
@@ -32741,7 +32715,7 @@
       </c>
     </row>
     <row r="650" spans="1:16">
-      <c r="A650" s="1">
+      <c r="A650">
         <v>5384194</v>
       </c>
       <c r="B650" t="s">
@@ -32791,7 +32765,7 @@
       </c>
     </row>
     <row r="651" spans="1:16">
-      <c r="A651" s="1">
+      <c r="A651">
         <v>5384210</v>
       </c>
       <c r="B651" t="s">
@@ -32841,7 +32815,7 @@
       </c>
     </row>
     <row r="652" spans="1:16">
-      <c r="A652" s="1">
+      <c r="A652">
         <v>5384211</v>
       </c>
       <c r="B652" t="s">
@@ -32891,7 +32865,7 @@
       </c>
     </row>
     <row r="653" spans="1:16">
-      <c r="A653" s="1">
+      <c r="A653">
         <v>5388272</v>
       </c>
       <c r="B653" t="s">
@@ -32941,7 +32915,7 @@
       </c>
     </row>
     <row r="654" spans="1:16">
-      <c r="A654" s="1">
+      <c r="A654">
         <v>5388273</v>
       </c>
       <c r="B654" t="s">
@@ -32991,7 +32965,7 @@
       </c>
     </row>
     <row r="655" spans="1:16">
-      <c r="A655" s="1">
+      <c r="A655">
         <v>5388274</v>
       </c>
       <c r="B655" t="s">
@@ -33041,7 +33015,7 @@
       </c>
     </row>
     <row r="656" spans="1:16">
-      <c r="A656" s="1">
+      <c r="A656">
         <v>5390931</v>
       </c>
       <c r="B656" t="s">
@@ -33091,7 +33065,7 @@
       </c>
     </row>
     <row r="657" spans="1:16">
-      <c r="A657" s="1">
+      <c r="A657">
         <v>5390932</v>
       </c>
       <c r="B657" t="s">
@@ -33138,7 +33112,7 @@
       </c>
     </row>
     <row r="658" spans="1:16">
-      <c r="A658" s="1">
+      <c r="A658">
         <v>5390933</v>
       </c>
       <c r="B658" t="s">
@@ -33188,7 +33162,7 @@
       </c>
     </row>
     <row r="659" spans="1:16">
-      <c r="A659" s="1">
+      <c r="A659">
         <v>5391870</v>
       </c>
       <c r="B659" t="s">
@@ -33238,7 +33212,7 @@
       </c>
     </row>
     <row r="660" spans="1:16">
-      <c r="A660" s="1">
+      <c r="A660">
         <v>5391871</v>
       </c>
       <c r="B660" t="s">
@@ -33288,7 +33262,7 @@
       </c>
     </row>
     <row r="661" spans="1:16">
-      <c r="A661" s="1">
+      <c r="A661">
         <v>5392149</v>
       </c>
       <c r="B661" t="s">
@@ -33338,7 +33312,7 @@
       </c>
     </row>
     <row r="662" spans="1:16">
-      <c r="A662" s="1">
+      <c r="A662">
         <v>5392150</v>
       </c>
       <c r="B662" t="s">
@@ -33388,7 +33362,7 @@
       </c>
     </row>
     <row r="663" spans="1:16">
-      <c r="A663" s="1">
+      <c r="A663">
         <v>5392151</v>
       </c>
       <c r="B663" t="s">
@@ -33438,7 +33412,7 @@
       </c>
     </row>
     <row r="664" spans="1:16">
-      <c r="A664" s="1">
+      <c r="A664">
         <v>5397869</v>
       </c>
       <c r="B664" t="s">
@@ -33488,7 +33462,7 @@
       </c>
     </row>
     <row r="665" spans="1:16">
-      <c r="A665" s="1">
+      <c r="A665">
         <v>5397870</v>
       </c>
       <c r="B665" t="s">
@@ -33535,7 +33509,7 @@
       </c>
     </row>
     <row r="666" spans="1:16">
-      <c r="A666" s="1">
+      <c r="A666">
         <v>5397871</v>
       </c>
       <c r="B666" t="s">
@@ -33585,7 +33559,7 @@
       </c>
     </row>
     <row r="667" spans="1:16">
-      <c r="A667" s="1">
+      <c r="A667">
         <v>5401450</v>
       </c>
       <c r="B667" t="s">
@@ -33635,7 +33609,7 @@
       </c>
     </row>
     <row r="668" spans="1:16">
-      <c r="A668" s="1">
+      <c r="A668">
         <v>5401451</v>
       </c>
       <c r="B668" t="s">
@@ -33685,7 +33659,7 @@
       </c>
     </row>
     <row r="669" spans="1:16">
-      <c r="A669" s="1">
+      <c r="A669">
         <v>5401701</v>
       </c>
       <c r="B669" t="s">
@@ -33735,7 +33709,7 @@
       </c>
     </row>
     <row r="670" spans="1:16">
-      <c r="A670" s="1">
+      <c r="A670">
         <v>5401702</v>
       </c>
       <c r="B670" t="s">
@@ -33785,7 +33759,7 @@
       </c>
     </row>
     <row r="671" spans="1:16">
-      <c r="A671" s="1">
+      <c r="A671">
         <v>5401703</v>
       </c>
       <c r="B671" t="s">
@@ -33835,7 +33809,7 @@
       </c>
     </row>
     <row r="672" spans="1:16">
-      <c r="A672" s="1">
+      <c r="A672">
         <v>5402427</v>
       </c>
       <c r="B672" t="s">
@@ -33885,7 +33859,7 @@
       </c>
     </row>
     <row r="673" spans="1:16">
-      <c r="A673" s="1">
+      <c r="A673">
         <v>5402428</v>
       </c>
       <c r="B673" t="s">
@@ -33935,7 +33909,7 @@
       </c>
     </row>
     <row r="674" spans="1:16">
-      <c r="A674" s="1">
+      <c r="A674">
         <v>5402429</v>
       </c>
       <c r="B674" t="s">
@@ -33985,7 +33959,7 @@
       </c>
     </row>
     <row r="675" spans="1:16">
-      <c r="A675" s="1">
+      <c r="A675">
         <v>5402430</v>
       </c>
       <c r="B675" t="s">
@@ -34035,7 +34009,7 @@
       </c>
     </row>
     <row r="676" spans="1:16">
-      <c r="A676" s="1">
+      <c r="A676">
         <v>5404667</v>
       </c>
       <c r="B676" t="s">
@@ -34085,7 +34059,7 @@
       </c>
     </row>
     <row r="677" spans="1:16">
-      <c r="A677" s="1">
+      <c r="A677">
         <v>5404668</v>
       </c>
       <c r="B677" t="s">
@@ -34132,7 +34106,7 @@
       </c>
     </row>
     <row r="678" spans="1:16">
-      <c r="A678" s="1">
+      <c r="A678">
         <v>5404669</v>
       </c>
       <c r="B678" t="s">
@@ -34182,7 +34156,7 @@
       </c>
     </row>
     <row r="679" spans="1:16">
-      <c r="A679" s="1">
+      <c r="A679">
         <v>5404670</v>
       </c>
       <c r="B679" t="s">
@@ -34232,7 +34206,7 @@
       </c>
     </row>
     <row r="680" spans="1:16">
-      <c r="A680" s="1">
+      <c r="A680">
         <v>5405051</v>
       </c>
       <c r="B680" t="s">
@@ -34282,7 +34256,7 @@
       </c>
     </row>
     <row r="681" spans="1:16">
-      <c r="A681" s="1">
+      <c r="A681">
         <v>5405052</v>
       </c>
       <c r="B681" t="s">
@@ -34332,7 +34306,7 @@
       </c>
     </row>
     <row r="682" spans="1:16">
-      <c r="A682" s="1">
+      <c r="A682">
         <v>5405443</v>
       </c>
       <c r="B682" t="s">
@@ -34382,7 +34356,7 @@
       </c>
     </row>
     <row r="683" spans="1:16">
-      <c r="A683" s="1">
+      <c r="A683">
         <v>5405444</v>
       </c>
       <c r="B683" t="s">
@@ -34429,7 +34403,7 @@
       </c>
     </row>
     <row r="684" spans="1:16">
-      <c r="A684" s="1">
+      <c r="A684">
         <v>5405445</v>
       </c>
       <c r="B684" t="s">
@@ -34479,7 +34453,7 @@
       </c>
     </row>
     <row r="685" spans="1:16">
-      <c r="A685" s="1">
+      <c r="A685">
         <v>5405446</v>
       </c>
       <c r="B685" t="s">
@@ -34529,7 +34503,7 @@
       </c>
     </row>
     <row r="686" spans="1:16">
-      <c r="A686" s="1">
+      <c r="A686">
         <v>5407142</v>
       </c>
       <c r="B686" t="s">
@@ -34579,7 +34553,7 @@
       </c>
     </row>
     <row r="687" spans="1:16">
-      <c r="A687" s="1">
+      <c r="A687">
         <v>5407143</v>
       </c>
       <c r="B687" t="s">
@@ -34629,7 +34603,7 @@
       </c>
     </row>
     <row r="688" spans="1:16">
-      <c r="A688" s="1">
+      <c r="A688">
         <v>5407144</v>
       </c>
       <c r="B688" t="s">
@@ -34679,7 +34653,7 @@
       </c>
     </row>
     <row r="689" spans="1:16">
-      <c r="A689" s="1">
+      <c r="A689">
         <v>5407865</v>
       </c>
       <c r="B689" t="s">
@@ -34729,7 +34703,7 @@
       </c>
     </row>
     <row r="690" spans="1:16">
-      <c r="A690" s="1">
+      <c r="A690">
         <v>5407866</v>
       </c>
       <c r="B690" t="s">
@@ -34779,7 +34753,7 @@
       </c>
     </row>
     <row r="691" spans="1:16">
-      <c r="A691" s="1">
+      <c r="A691">
         <v>5407867</v>
       </c>
       <c r="B691" t="s">
@@ -34826,7 +34800,7 @@
       </c>
     </row>
     <row r="692" spans="1:16">
-      <c r="A692" s="1">
+      <c r="A692">
         <v>5407868</v>
       </c>
       <c r="B692" t="s">
@@ -34873,7 +34847,7 @@
       </c>
     </row>
     <row r="693" spans="1:16">
-      <c r="A693" s="1">
+      <c r="A693">
         <v>5407869</v>
       </c>
       <c r="B693" t="s">
@@ -34923,7 +34897,7 @@
       </c>
     </row>
     <row r="694" spans="1:16">
-      <c r="A694" s="1">
+      <c r="A694">
         <v>5410018</v>
       </c>
       <c r="B694" t="s">
@@ -34973,7 +34947,7 @@
       </c>
     </row>
     <row r="695" spans="1:16">
-      <c r="A695" s="1">
+      <c r="A695">
         <v>5410019</v>
       </c>
       <c r="B695" t="s">
@@ -35020,7 +34994,7 @@
       </c>
     </row>
     <row r="696" spans="1:16">
-      <c r="A696" s="1">
+      <c r="A696">
         <v>5410020</v>
       </c>
       <c r="B696" t="s">
@@ -35070,7 +35044,7 @@
       </c>
     </row>
     <row r="697" spans="1:16">
-      <c r="A697" s="1">
+      <c r="A697">
         <v>5410021</v>
       </c>
       <c r="B697" t="s">
@@ -35120,7 +35094,7 @@
       </c>
     </row>
     <row r="698" spans="1:16">
-      <c r="A698" s="1">
+      <c r="A698">
         <v>5410486</v>
       </c>
       <c r="B698" t="s">
@@ -35170,7 +35144,7 @@
       </c>
     </row>
     <row r="699" spans="1:16">
-      <c r="A699" s="1">
+      <c r="A699">
         <v>5410487</v>
       </c>
       <c r="B699" t="s">
@@ -35220,7 +35194,7 @@
       </c>
     </row>
     <row r="700" spans="1:16">
-      <c r="A700" s="1">
+      <c r="A700">
         <v>5410488</v>
       </c>
       <c r="B700" t="s">
@@ -35270,7 +35244,7 @@
       </c>
     </row>
     <row r="701" spans="1:16">
-      <c r="A701" s="1">
+      <c r="A701">
         <v>5412242</v>
       </c>
       <c r="B701" t="s">
@@ -35320,7 +35294,7 @@
       </c>
     </row>
     <row r="702" spans="1:16">
-      <c r="A702" s="1">
+      <c r="A702">
         <v>5412243</v>
       </c>
       <c r="B702" t="s">
@@ -35367,7 +35341,7 @@
       </c>
     </row>
     <row r="703" spans="1:16">
-      <c r="A703" s="1">
+      <c r="A703">
         <v>5412244</v>
       </c>
       <c r="B703" t="s">
@@ -35417,7 +35391,7 @@
       </c>
     </row>
     <row r="704" spans="1:16">
-      <c r="A704" s="1">
+      <c r="A704">
         <v>5412245</v>
       </c>
       <c r="B704" t="s">
@@ -35467,7 +35441,7 @@
       </c>
     </row>
     <row r="705" spans="1:16">
-      <c r="A705" s="1">
+      <c r="A705">
         <v>5412394</v>
       </c>
       <c r="B705" t="s">
@@ -35517,7 +35491,7 @@
       </c>
     </row>
     <row r="706" spans="1:16">
-      <c r="A706" s="1">
+      <c r="A706">
         <v>5412505</v>
       </c>
       <c r="B706" t="s">
@@ -35567,7 +35541,7 @@
       </c>
     </row>
     <row r="707" spans="1:16">
-      <c r="A707" s="1">
+      <c r="A707">
         <v>5412506</v>
       </c>
       <c r="B707" t="s">
@@ -35617,7 +35591,7 @@
       </c>
     </row>
     <row r="708" spans="1:16">
-      <c r="A708" s="1">
+      <c r="A708">
         <v>5412507</v>
       </c>
       <c r="B708" t="s">
@@ -35667,7 +35641,7 @@
       </c>
     </row>
     <row r="709" spans="1:16">
-      <c r="A709" s="1">
+      <c r="A709">
         <v>5412508</v>
       </c>
       <c r="B709" t="s">
@@ -35717,7 +35691,7 @@
       </c>
     </row>
     <row r="710" spans="1:16">
-      <c r="A710" s="1">
+      <c r="A710">
         <v>5412547</v>
       </c>
       <c r="B710" t="s">
@@ -35767,7 +35741,7 @@
       </c>
     </row>
     <row r="711" spans="1:16">
-      <c r="A711" s="1">
+      <c r="A711">
         <v>5412548</v>
       </c>
       <c r="B711" t="s">
@@ -35817,7 +35791,7 @@
       </c>
     </row>
     <row r="712" spans="1:16">
-      <c r="A712" s="1">
+      <c r="A712">
         <v>5412549</v>
       </c>
       <c r="B712" t="s">
@@ -35867,7 +35841,7 @@
       </c>
     </row>
     <row r="713" spans="1:16">
-      <c r="A713" s="1">
+      <c r="A713">
         <v>5412550</v>
       </c>
       <c r="B713" t="s">
